--- a/response_spectrum_classic.xlsx
+++ b/response_spectrum_classic.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F201"/>
+  <dimension ref="A1:F301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -491,3982 +491,5982 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.03005025125628141</v>
+        <v>0.02</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3395346597248804</v>
+        <v>0.3227176295268882</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3402720602016389</v>
+        <v>0.3227720224417558</v>
       </c>
       <c r="D3" t="n">
-        <v>1.593020484155929</v>
+        <v>1.007724518976466</v>
       </c>
       <c r="E3" t="n">
-        <v>0.667631493940795</v>
+        <v>0.3211670881021957</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007618853092011867</v>
+        <v>0.00320768676940014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.05010050251256282</v>
+        <v>0.03</v>
       </c>
       <c r="B4" t="n">
-        <v>0.3454144011518372</v>
+        <v>0.3393335051456983</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3467151680327286</v>
+        <v>0.340046439561045</v>
       </c>
       <c r="D4" t="n">
-        <v>2.701914869039673</v>
+        <v>1.589414376339747</v>
       </c>
       <c r="E4" t="n">
-        <v>1.527257720322036</v>
+        <v>0.6675015004356148</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02154437376379354</v>
+        <v>0.00758889463847378</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.07015075376884422</v>
+        <v>0.04</v>
       </c>
       <c r="B5" t="n">
-        <v>0.4738984352219885</v>
+        <v>0.3354269394781969</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4800457831138537</v>
+        <v>0.335469896596146</v>
       </c>
       <c r="D5" t="n">
-        <v>5.190470840810566</v>
+        <v>2.094821728412895</v>
       </c>
       <c r="E5" t="n">
-        <v>2.809572776754653</v>
+        <v>1.169894308087331</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0579507724341673</v>
+        <v>0.0133360493189288</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.09020100502512562</v>
+        <v>0.05</v>
       </c>
       <c r="B6" t="n">
-        <v>0.4990034305606608</v>
+        <v>0.3456988853602061</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4963359740427941</v>
+        <v>0.3466167457221837</v>
       </c>
       <c r="D6" t="n">
-        <v>7.027551660635983</v>
+        <v>2.698715619216649</v>
       </c>
       <c r="E6" t="n">
-        <v>5.002803543706971</v>
+        <v>1.517069071687881</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1008870806231083</v>
+        <v>0.02147569653988175</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.110251256281407</v>
+        <v>0.06</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5242782513964954</v>
+        <v>0.432632190376016</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5209333507440587</v>
+        <v>0.4318310561137615</v>
       </c>
       <c r="D7" t="n">
-        <v>9.024736451970771</v>
+        <v>4.052837769472533</v>
       </c>
       <c r="E7" t="n">
-        <v>6.569062390239437</v>
+        <v>1.955837980347877</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1583573430981648</v>
+        <v>0.0387017498736651</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1303015075376885</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8" t="n">
-        <v>0.6531119354008983</v>
+        <v>0.4736980469561902</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6611053475076856</v>
+        <v>0.4797244962011998</v>
       </c>
       <c r="D8" t="n">
-        <v>13.28697750685487</v>
+        <v>5.177126456434756</v>
       </c>
       <c r="E8" t="n">
-        <v>11.069002649745</v>
+        <v>2.800769640385889</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2755470537824554</v>
+        <v>0.05767756865873935</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1503517587939699</v>
+        <v>0.08</v>
       </c>
       <c r="B9" t="n">
-        <v>0.8778174741097404</v>
+        <v>0.5013392583964197</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8833712814558045</v>
+        <v>0.4988943849969283</v>
       </c>
       <c r="D9" t="n">
-        <v>20.60638803108626</v>
+        <v>6.261967947052698</v>
       </c>
       <c r="E9" t="n">
-        <v>17.13073255022014</v>
+        <v>4.300793679950578</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4930949082982817</v>
+        <v>0.07972985218051558</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1704020100502513</v>
+        <v>0.09</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8228638991759148</v>
+        <v>0.4961094421336757</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8299618410039236</v>
+        <v>0.4934407704879918</v>
       </c>
       <c r="D10" t="n">
-        <v>21.89232373494626</v>
+        <v>6.971225660960805</v>
       </c>
       <c r="E10" t="n">
-        <v>19.83584764370002</v>
+        <v>4.975908036072031</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5937268736675575</v>
+        <v>0.09985545210158796</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1904522613065327</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11" t="n">
-        <v>1.004727113470562</v>
+        <v>0.5566898685442127</v>
       </c>
       <c r="C11" t="n">
-        <v>1.014433544243942</v>
+        <v>0.562381455109468</v>
       </c>
       <c r="D11" t="n">
-        <v>29.87606494393589</v>
+        <v>8.691654540537707</v>
       </c>
       <c r="E11" t="n">
-        <v>26.69520860319555</v>
+        <v>6.3412508066022</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9055859169093239</v>
+        <v>0.1383319783773692</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2105025125628141</v>
+        <v>0.11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9064512643341384</v>
+        <v>0.5215348735817429</v>
       </c>
       <c r="C12" t="n">
-        <v>0.9138502489079248</v>
+        <v>0.5176148887814731</v>
       </c>
       <c r="D12" t="n">
-        <v>29.79139789808241</v>
+        <v>8.957053700755559</v>
       </c>
       <c r="E12" t="n">
-        <v>27.24517110130759</v>
+        <v>6.564341819318925</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9980867670955107</v>
+        <v>0.1568115309216282</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2305527638190955</v>
+        <v>0.12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.6846405271753231</v>
+        <v>0.6083915703243868</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6878676583648613</v>
+        <v>0.6093470216208289</v>
       </c>
       <c r="D13" t="n">
-        <v>24.64461712380205</v>
+        <v>11.39865405159214</v>
       </c>
       <c r="E13" t="n">
-        <v>21.00112002880764</v>
+        <v>7.760532930924318</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9043000187601452</v>
+        <v>0.217698256428642</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2506030150753769</v>
+        <v>0.13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.812593434364788</v>
+        <v>0.6532668384692641</v>
       </c>
       <c r="C14" t="n">
-        <v>0.818573904785849</v>
+        <v>0.6606018753519735</v>
       </c>
       <c r="D14" t="n">
-        <v>31.79426134782918</v>
+        <v>13.25937654819577</v>
       </c>
       <c r="E14" t="n">
-        <v>27.77547510878824</v>
+        <v>10.9951748466315</v>
       </c>
       <c r="F14" t="n">
-        <v>1.268104849105125</v>
+        <v>0.2743383915950743</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2706532663316583</v>
+        <v>0.14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.8074490625876378</v>
+        <v>0.6095733712888601</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8104850044605236</v>
+        <v>0.6183636804459399</v>
       </c>
       <c r="D15" t="n">
-        <v>34.1206696774131</v>
+        <v>13.32426193401449</v>
       </c>
       <c r="E15" t="n">
-        <v>33.02011046091847</v>
+        <v>11.65673872915661</v>
       </c>
       <c r="F15" t="n">
-        <v>1.469775320339995</v>
+        <v>0.2968871009789416</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2907035175879397</v>
+        <v>0.15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.7115651298982658</v>
+        <v>0.8714614074110063</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7125405193069206</v>
+        <v>0.8749623765424022</v>
       </c>
       <c r="D16" t="n">
-        <v>32.2963976223394</v>
+        <v>20.40932104198791</v>
       </c>
       <c r="E16" t="n">
-        <v>31.58573060747254</v>
+        <v>16.89578390484754</v>
       </c>
       <c r="F16" t="n">
-        <v>1.494254257232348</v>
+        <v>0.4872366493472713</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.3107537688442211</v>
+        <v>0.16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.8178462264878475</v>
+        <v>0.746131961322542</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8227425059541733</v>
+        <v>0.748557020821411</v>
       </c>
       <c r="D17" t="n">
-        <v>39.68050564800741</v>
+        <v>18.63909258180962</v>
       </c>
       <c r="E17" t="n">
-        <v>40.75529409433455</v>
+        <v>16.52036367454863</v>
       </c>
       <c r="F17" t="n">
-        <v>1.962518384691382</v>
+        <v>0.4746405950627965</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3308040201005025</v>
+        <v>0.17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.8784552135899102</v>
+        <v>0.8181383202338651</v>
       </c>
       <c r="C18" t="n">
-        <v>0.880064995558691</v>
+        <v>0.8239939540356942</v>
       </c>
       <c r="D18" t="n">
-        <v>45.37112442020452</v>
+        <v>21.71524807799242</v>
       </c>
       <c r="E18" t="n">
-        <v>47.70232409254201</v>
+        <v>19.62196841337854</v>
       </c>
       <c r="F18" t="n">
-        <v>2.388748639568773</v>
+        <v>0.5875351422534765</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.3508542713567839</v>
+        <v>0.18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.8682708405023277</v>
+        <v>0.9391352270400052</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8709439117128095</v>
+        <v>0.9397305878770792</v>
       </c>
       <c r="D19" t="n">
-        <v>47.56320629517188</v>
+        <v>26.39306184416252</v>
       </c>
       <c r="E19" t="n">
-        <v>48.55585257316179</v>
+        <v>22.93367981388769</v>
       </c>
       <c r="F19" t="n">
-        <v>2.655938552220701</v>
+        <v>0.7561055260491411</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3709045226130653</v>
+        <v>0.19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.8595668879233145</v>
+        <v>1.005644069872837</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8634677448556579</v>
+        <v>1.013311553864508</v>
       </c>
       <c r="D20" t="n">
-        <v>49.77725520583492</v>
+        <v>29.83232055394172</v>
       </c>
       <c r="E20" t="n">
-        <v>52.30640071283052</v>
+        <v>26.5519382446542</v>
       </c>
       <c r="F20" t="n">
-        <v>2.938415497313491</v>
+        <v>0.902112643211737</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3909547738693467</v>
+        <v>0.2</v>
       </c>
       <c r="B21" t="n">
-        <v>0.8718183901283312</v>
+        <v>0.9974130959522827</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8768492460880236</v>
+        <v>0.9959285513625608</v>
       </c>
       <c r="D21" t="n">
-        <v>53.2159335673108</v>
+        <v>31.14542065188283</v>
       </c>
       <c r="E21" t="n">
-        <v>56.54128713785779</v>
+        <v>28.61028955142238</v>
       </c>
       <c r="F21" t="n">
-        <v>3.31122229520765</v>
+        <v>0.9913895302847108</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4110050251256281</v>
+        <v>0.21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.8917996058534802</v>
+        <v>0.9137956320067434</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8952006531325777</v>
+        <v>0.9199441017601433</v>
       </c>
       <c r="D22" t="n">
-        <v>57.22733829466408</v>
+        <v>29.9610832637072</v>
       </c>
       <c r="E22" t="n">
-        <v>60.65778012993819</v>
+        <v>27.42882254634729</v>
       </c>
       <c r="F22" t="n">
-        <v>3.743439428214044</v>
+        <v>1.00137544537944</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4310552763819095</v>
+        <v>0.22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9193301862922137</v>
+        <v>0.7549012485263947</v>
       </c>
       <c r="C23" t="n">
-        <v>0.9230640834424598</v>
+        <v>0.7548973921925537</v>
       </c>
       <c r="D23" t="n">
-        <v>61.87192452703533</v>
+        <v>25.92996696608646</v>
       </c>
       <c r="E23" t="n">
-        <v>64.47972221596567</v>
+        <v>22.87766015298615</v>
       </c>
       <c r="F23" t="n">
-        <v>4.244697271112901</v>
+        <v>0.9079141317096877</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.451105527638191</v>
+        <v>0.23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.9675734885985027</v>
+        <v>0.6882492014865014</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9715277594121201</v>
+        <v>0.6906479273119984</v>
       </c>
       <c r="D24" t="n">
-        <v>68.14770708429118</v>
+        <v>24.71511816688822</v>
       </c>
       <c r="E24" t="n">
-        <v>68.06832619007859</v>
+        <v>21.0084368622831</v>
       </c>
       <c r="F24" t="n">
-        <v>4.892710601176193</v>
+        <v>0.9047126418329295</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4711557788944724</v>
+        <v>0.24</v>
       </c>
       <c r="B25" t="n">
-        <v>1.013438333958546</v>
+        <v>0.6937426567373784</v>
       </c>
       <c r="C25" t="n">
-        <v>1.018585198838665</v>
+        <v>0.6952351362395528</v>
       </c>
       <c r="D25" t="n">
-        <v>74.55057355035443</v>
+        <v>25.9955361997061</v>
       </c>
       <c r="E25" t="n">
-        <v>70.9619132395955</v>
+        <v>22.91270288229133</v>
       </c>
       <c r="F25" t="n">
-        <v>5.590306799961923</v>
+        <v>0.9929563402818071</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.4912060301507538</v>
+        <v>0.25</v>
       </c>
       <c r="B26" t="n">
-        <v>1.040633323653121</v>
+        <v>0.8077743178156993</v>
       </c>
       <c r="C26" t="n">
-        <v>1.045588260028655</v>
+        <v>0.8127422470854396</v>
       </c>
       <c r="D26" t="n">
-        <v>79.80875898565493</v>
+        <v>31.52965283674355</v>
       </c>
       <c r="E26" t="n">
-        <v>72.84294627469582</v>
+        <v>27.38575515600871</v>
       </c>
       <c r="F26" t="n">
-        <v>6.239278607270491</v>
+        <v>1.254525025734784</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5112562814070352</v>
+        <v>0.26</v>
       </c>
       <c r="B27" t="n">
-        <v>1.037797467719531</v>
+        <v>0.8557128870732853</v>
       </c>
       <c r="C27" t="n">
-        <v>1.044797008994881</v>
+        <v>0.8591223872078683</v>
       </c>
       <c r="D27" t="n">
-        <v>82.84005957859767</v>
+        <v>34.73686009666401</v>
       </c>
       <c r="E27" t="n">
-        <v>80.71218545369948</v>
+        <v>32.11303264733738</v>
       </c>
       <c r="F27" t="n">
-        <v>6.740609856484148</v>
+        <v>1.437421177887679</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5313065326633166</v>
+        <v>0.27</v>
       </c>
       <c r="B28" t="n">
-        <v>1.003471138834043</v>
+        <v>0.8126635375188858</v>
       </c>
       <c r="C28" t="n">
-        <v>1.008359653960635</v>
+        <v>0.8146893674172575</v>
       </c>
       <c r="D28" t="n">
-        <v>83.24136264887103</v>
+        <v>34.25813192819064</v>
       </c>
       <c r="E28" t="n">
-        <v>86.76315247598896</v>
+        <v>33.08262737524693</v>
       </c>
       <c r="F28" t="n">
-        <v>7.038894700846246</v>
+        <v>1.472134780115772</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.551356783919598</v>
+        <v>0.28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.9440715385483934</v>
+        <v>0.736516726413934</v>
       </c>
       <c r="C29" t="n">
-        <v>0.9488743351636197</v>
+        <v>0.7394026681436608</v>
       </c>
       <c r="D29" t="n">
-        <v>81.26934629831646</v>
+        <v>32.19806587276849</v>
       </c>
       <c r="E29" t="n">
-        <v>90.87581337806826</v>
+        <v>31.44878094463028</v>
       </c>
       <c r="F29" t="n">
-        <v>7.131479212476317</v>
+        <v>1.434854775661879</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5714070351758794</v>
+        <v>0.29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.8693584667055816</v>
+        <v>0.7105996599796834</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8734757280870423</v>
+        <v>0.7113117323645771</v>
       </c>
       <c r="D30" t="n">
-        <v>77.55925168609957</v>
+        <v>32.17452412817116</v>
       </c>
       <c r="E30" t="n">
-        <v>92.12993253287858</v>
+        <v>31.45224397075974</v>
       </c>
       <c r="F30" t="n">
-        <v>7.053413179740758</v>
+        <v>1.48501302142209</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.5914572864321608</v>
+        <v>0.3</v>
       </c>
       <c r="B31" t="n">
-        <v>0.8256557814184355</v>
+        <v>0.7488909010592865</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8305571713926649</v>
+        <v>0.7554649903866115</v>
       </c>
       <c r="D31" t="n">
-        <v>76.24503212172888</v>
+        <v>35.07752539621995</v>
       </c>
       <c r="E31" t="n">
-        <v>90.40506045862118</v>
+        <v>34.96605876678102</v>
       </c>
       <c r="F31" t="n">
-        <v>7.177200352681207</v>
+        <v>1.67482846747197</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6115075376884422</v>
+        <v>0.31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.7802038121392589</v>
+        <v>0.8142252712753345</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7848859466850422</v>
+        <v>0.8179400656381876</v>
       </c>
       <c r="D32" t="n">
-        <v>74.49017965338913</v>
+        <v>39.40899959843643</v>
       </c>
       <c r="E32" t="n">
-        <v>86.72238187882229</v>
+        <v>40.36185303124925</v>
       </c>
       <c r="F32" t="n">
-        <v>7.249715568592848</v>
+        <v>1.94436249740328</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6315577889447236</v>
+        <v>0.32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.7297969937774037</v>
+        <v>0.8575287709321373</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7343365896338915</v>
+        <v>0.863701805737107</v>
       </c>
       <c r="D33" t="n">
-        <v>71.96217891461868</v>
+        <v>42.84378362411433</v>
       </c>
       <c r="E33" t="n">
-        <v>81.54501836572804</v>
+        <v>44.75299443909946</v>
       </c>
       <c r="F33" t="n">
-        <v>7.233317558059118</v>
+        <v>2.182015982251966</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.651608040201005</v>
+        <v>0.33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.6779404082138821</v>
+        <v>0.877581244058393</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6823298594596751</v>
+        <v>0.8806201696626371</v>
       </c>
       <c r="D34" t="n">
-        <v>68.97109071087179</v>
+        <v>45.21582004184928</v>
       </c>
       <c r="E34" t="n">
-        <v>75.40570662251564</v>
+        <v>47.61002659273822</v>
       </c>
       <c r="F34" t="n">
-        <v>7.152760113136096</v>
+        <v>2.374786017652588</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.6716582914572865</v>
+        <v>0.34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.6268985843905091</v>
+        <v>0.8764207977253111</v>
       </c>
       <c r="C35" t="n">
-        <v>0.6310696778462674</v>
+        <v>0.8800826361913343</v>
       </c>
       <c r="D35" t="n">
-        <v>65.74077333461162</v>
+        <v>46.52439464729369</v>
       </c>
       <c r="E35" t="n">
-        <v>69.00635754862473</v>
+        <v>48.74834627301653</v>
       </c>
       <c r="F35" t="n">
-        <v>7.027539908229532</v>
+        <v>2.517559710041469</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.6917085427135679</v>
+        <v>0.35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.5779341415545693</v>
+        <v>0.8684637072754642</v>
       </c>
       <c r="C36" t="n">
-        <v>0.5821966676090947</v>
+        <v>0.8723381429051591</v>
       </c>
       <c r="D36" t="n">
-        <v>62.41523781211244</v>
+        <v>47.45793722688749</v>
       </c>
       <c r="E36" t="n">
-        <v>67.18189258109291</v>
+        <v>48.58916471423539</v>
       </c>
       <c r="F36" t="n">
-        <v>6.871220739073946</v>
+        <v>2.643607854511407</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.7117587939698493</v>
+        <v>0.36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.5334211157173384</v>
+        <v>0.861752002505936</v>
       </c>
       <c r="C37" t="n">
-        <v>0.537561878679445</v>
+        <v>0.8637493791767559</v>
       </c>
       <c r="D37" t="n">
-        <v>59.27781460550187</v>
+        <v>48.43663242865707</v>
       </c>
       <c r="E37" t="n">
-        <v>65.62448713950553</v>
+        <v>50.07144330028041</v>
       </c>
       <c r="F37" t="n">
-        <v>6.714986709777524</v>
+        <v>2.775214611988549</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7318090452261307</v>
+        <v>0.37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.4919797588807262</v>
+        <v>0.8585923716563145</v>
       </c>
       <c r="C38" t="n">
-        <v>0.4956577565678962</v>
+        <v>0.8634915521397928</v>
       </c>
       <c r="D38" t="n">
-        <v>56.21266138669792</v>
+        <v>49.59956740158343</v>
       </c>
       <c r="E38" t="n">
-        <v>64.11538477547084</v>
+        <v>52.08902141526288</v>
       </c>
       <c r="F38" t="n">
-        <v>6.54714639913825</v>
+        <v>2.920786041057206</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7518592964824121</v>
+        <v>0.38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.4615424202833734</v>
+        <v>0.8641957445093493</v>
       </c>
       <c r="C39" t="n">
-        <v>0.4629754739367947</v>
+        <v>0.8659503999421959</v>
       </c>
       <c r="D39" t="n">
-        <v>54.1797923408766</v>
+        <v>51.27254312714279</v>
       </c>
       <c r="E39" t="n">
-        <v>62.66893348794309</v>
+        <v>54.36187973492833</v>
       </c>
       <c r="F39" t="n">
-        <v>6.483269004724</v>
+        <v>3.100905899759321</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7719095477386935</v>
+        <v>0.39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.4463280107604389</v>
+        <v>0.8707961526947642</v>
       </c>
       <c r="C40" t="n">
-        <v>0.4475564905970517</v>
+        <v>0.8756518081405629</v>
       </c>
       <c r="D40" t="n">
-        <v>53.7910095278185</v>
+        <v>53.02372662458347</v>
       </c>
       <c r="E40" t="n">
-        <v>61.27529730925022</v>
+        <v>56.30801915148783</v>
       </c>
       <c r="F40" t="n">
-        <v>6.608398735205305</v>
+        <v>3.291205395447762</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.7919597989949749</v>
+        <v>0.4</v>
       </c>
       <c r="B41" t="n">
-        <v>0.4369715546943461</v>
+        <v>0.8820944955142866</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4382228324967862</v>
+        <v>0.8856653734951065</v>
       </c>
       <c r="D41" t="n">
-        <v>54.03130320643428</v>
+        <v>55.08891797991227</v>
       </c>
       <c r="E41" t="n">
-        <v>60.10815749402921</v>
+        <v>58.64329810228936</v>
       </c>
       <c r="F41" t="n">
-        <v>6.810338695232946</v>
+        <v>3.507069442434811</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8120100502512563</v>
+        <v>0.41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.4562251883572233</v>
+        <v>0.8914700975806392</v>
       </c>
       <c r="C42" t="n">
-        <v>0.458587184912994</v>
+        <v>0.893335594742115</v>
       </c>
       <c r="D42" t="n">
-        <v>57.84020222739829</v>
+        <v>57.06630799798257</v>
       </c>
       <c r="E42" t="n">
-        <v>58.98755703543406</v>
+        <v>60.49912353098675</v>
       </c>
       <c r="F42" t="n">
-        <v>7.475002442398934</v>
+        <v>3.72377785077223</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.8320603015075377</v>
+        <v>0.42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.5100409928371085</v>
+        <v>0.8976040979914519</v>
       </c>
       <c r="C43" t="n">
-        <v>0.5126136710527347</v>
+        <v>0.9031268800750635</v>
       </c>
       <c r="D43" t="n">
-        <v>66.25963258193067</v>
+        <v>58.86040636615392</v>
       </c>
       <c r="E43" t="n">
-        <v>62.19061844206371</v>
+        <v>62.5650268009602</v>
       </c>
       <c r="F43" t="n">
-        <v>8.774531892430803</v>
+        <v>3.934528342739847</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8521105527638191</v>
+        <v>0.43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.5534008773839386</v>
+        <v>0.9171685542594492</v>
       </c>
       <c r="C44" t="n">
-        <v>0.5560584520902658</v>
+        <v>0.9202575570389327</v>
       </c>
       <c r="D44" t="n">
-        <v>73.6249352977047</v>
+        <v>61.57533039828987</v>
       </c>
       <c r="E44" t="n">
-        <v>67.78227740632779</v>
+        <v>64.32159316587025</v>
       </c>
       <c r="F44" t="n">
-        <v>9.984837506231205</v>
+        <v>4.214007828323926</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.8721608040201005</v>
+        <v>0.44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.57517579959719</v>
+        <v>0.939115392950381</v>
       </c>
       <c r="C45" t="n">
-        <v>0.5783804499202821</v>
+        <v>0.9459944755434151</v>
       </c>
       <c r="D45" t="n">
-        <v>78.32245808483547</v>
+        <v>64.5150108417002</v>
       </c>
       <c r="E45" t="n">
-        <v>76.16319433024276</v>
+        <v>66.29681790289081</v>
       </c>
       <c r="F45" t="n">
-        <v>10.87183883277252</v>
+        <v>4.517868466796875</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.8922110552763819</v>
+        <v>0.45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.5711597041826438</v>
+        <v>0.9649541577550376</v>
       </c>
       <c r="C46" t="n">
-        <v>0.5738914155997723</v>
+        <v>0.9691932936776051</v>
       </c>
       <c r="D46" t="n">
-        <v>79.56357689837773</v>
+        <v>67.79666556296044</v>
       </c>
       <c r="E46" t="n">
-        <v>80.38772835683248</v>
+        <v>67.92991247779281</v>
       </c>
       <c r="F46" t="n">
-        <v>11.29801198525056</v>
+        <v>4.855578502271954</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.9122613065326634</v>
+        <v>0.46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.5409371939702765</v>
+        <v>0.986424953902956</v>
       </c>
       <c r="C47" t="n">
-        <v>0.5439808920886614</v>
+        <v>0.9947384400035931</v>
       </c>
       <c r="D47" t="n">
-        <v>77.04691208376856</v>
+        <v>70.84529628461031</v>
       </c>
       <c r="E47" t="n">
-        <v>79.75120198216263</v>
+        <v>69.68971651803822</v>
       </c>
       <c r="F47" t="n">
-        <v>11.18651022460398</v>
+        <v>5.186674385312585</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.9323115577889447</v>
+        <v>0.47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.4895999187407001</v>
+        <v>1.011189809828696</v>
       </c>
       <c r="C48" t="n">
-        <v>0.4920498010224106</v>
+        <v>1.016657537225544</v>
       </c>
       <c r="D48" t="n">
-        <v>71.26750325619976</v>
+        <v>74.2026954202628</v>
       </c>
       <c r="E48" t="n">
-        <v>78.15697825422757</v>
+        <v>70.80267763279578</v>
       </c>
       <c r="F48" t="n">
-        <v>10.57481416385945</v>
+        <v>5.550571110432269</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.9523618090452262</v>
+        <v>0.48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.5009432334852396</v>
+        <v>1.026861427966185</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5030912851367582</v>
+        <v>1.035051682606853</v>
       </c>
       <c r="D49" t="n">
-        <v>74.48685281633102</v>
+        <v>76.95595236514913</v>
       </c>
       <c r="E49" t="n">
-        <v>76.40898066478968</v>
+        <v>71.57943360867779</v>
       </c>
       <c r="F49" t="n">
-        <v>11.2902024101036</v>
+        <v>5.879001705243801</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>0.9724120603015076</v>
+        <v>0.49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.5016560120074851</v>
+        <v>1.04009283065387</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5046052493925179</v>
+        <v>1.045379433606531</v>
       </c>
       <c r="D50" t="n">
-        <v>76.16325510632927</v>
+        <v>79.57145911258077</v>
       </c>
       <c r="E50" t="n">
-        <v>79.44952872447702</v>
+        <v>72.31570819703801</v>
       </c>
       <c r="F50" t="n">
-        <v>11.78734418871694</v>
+        <v>6.205453612932915</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.992462311557789</v>
+        <v>0.5</v>
       </c>
       <c r="B51" t="n">
-        <v>0.4895473113364705</v>
+        <v>1.044040218630061</v>
       </c>
       <c r="C51" t="n">
-        <v>0.4925695221992974</v>
+        <v>1.05068230744053</v>
       </c>
       <c r="D51" t="n">
-        <v>75.85737887007367</v>
+        <v>81.50352125583234</v>
       </c>
       <c r="E51" t="n">
-        <v>85.18975435980951</v>
+        <v>76.36137334785055</v>
       </c>
       <c r="F51" t="n">
-        <v>11.98207372558024</v>
+        <v>6.48584414363054</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.01251256281407</v>
+        <v>0.51</v>
       </c>
       <c r="B52" t="n">
-        <v>0.46504423332891</v>
+        <v>1.0382511598806</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4677463550835116</v>
+        <v>1.045594907650815</v>
       </c>
       <c r="D52" t="n">
-        <v>73.5163307280237</v>
+        <v>82.67262740226806</v>
       </c>
       <c r="E52" t="n">
-        <v>87.73512588847913</v>
+        <v>80.27914829014482</v>
       </c>
       <c r="F52" t="n">
-        <v>11.84689051730852</v>
+        <v>6.710456227827375</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.032562814070352</v>
+        <v>0.52</v>
       </c>
       <c r="B53" t="n">
-        <v>0.456663626352542</v>
+        <v>1.026297642076093</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4593613188488147</v>
+        <v>1.031430833713667</v>
       </c>
       <c r="D53" t="n">
-        <v>73.6210556894591</v>
+        <v>83.32317567932155</v>
       </c>
       <c r="E53" t="n">
-        <v>87.49224325866459</v>
+        <v>83.62510389006873</v>
       </c>
       <c r="F53" t="n">
-        <v>12.09869846599531</v>
+        <v>6.895873547408778</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.052613065326633</v>
+        <v>0.53</v>
       </c>
       <c r="B54" t="n">
-        <v>0.4404740941681947</v>
+        <v>1.007044478151154</v>
       </c>
       <c r="C54" t="n">
-        <v>0.4433446304694427</v>
+        <v>1.012206591779463</v>
       </c>
       <c r="D54" t="n">
-        <v>72.38994829531732</v>
+        <v>83.33235611033754</v>
       </c>
       <c r="E54" t="n">
-        <v>84.41861027505402</v>
+        <v>86.37387625945829</v>
       </c>
       <c r="F54" t="n">
-        <v>12.12738470197606</v>
+        <v>7.029260889060794</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.072663316582915</v>
+        <v>0.54</v>
       </c>
       <c r="B55" t="n">
-        <v>0.4180767319277769</v>
+        <v>0.9806843897151031</v>
       </c>
       <c r="C55" t="n">
-        <v>0.4206074937051772</v>
+        <v>0.9858883752147521</v>
       </c>
       <c r="D55" t="n">
-        <v>70.0178168308734</v>
+        <v>82.68222616545377</v>
       </c>
       <c r="E55" t="n">
-        <v>79.39424867845294</v>
+        <v>88.82337809249837</v>
       </c>
       <c r="F55" t="n">
-        <v>11.95341852099748</v>
+        <v>7.106013900039969</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.092713567839196</v>
+        <v>0.55</v>
       </c>
       <c r="B56" t="n">
-        <v>0.3915638743216038</v>
+        <v>0.9488480258348136</v>
       </c>
       <c r="C56" t="n">
-        <v>0.3936067985200142</v>
+        <v>0.9538731418754176</v>
       </c>
       <c r="D56" t="n">
-        <v>66.80332691485111</v>
+        <v>81.47952468538283</v>
       </c>
       <c r="E56" t="n">
-        <v>72.57361401388819</v>
+        <v>90.67739196387855</v>
       </c>
       <c r="F56" t="n">
-        <v>11.61781773541583</v>
+        <v>7.132328012951233</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.112763819095477</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57" t="n">
-        <v>0.362663938453057</v>
+        <v>0.9131173305990963</v>
       </c>
       <c r="C57" t="n">
-        <v>0.3645881170488351</v>
+        <v>0.9178187741030697</v>
       </c>
       <c r="D57" t="n">
-        <v>63.0081181712141</v>
+        <v>79.83691586570328</v>
       </c>
       <c r="E57" t="n">
-        <v>65.06708855594188</v>
+        <v>91.6244046289158</v>
       </c>
       <c r="F57" t="n">
-        <v>11.15885506832074</v>
+        <v>7.115606288693528</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.132814070351759</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58" t="n">
-        <v>0.3322402919298109</v>
+        <v>0.8749911510966503</v>
       </c>
       <c r="C58" t="n">
-        <v>0.334109753688844</v>
+        <v>0.8792687716140032</v>
       </c>
       <c r="D58" t="n">
-        <v>58.76247417734027</v>
+        <v>77.86954833237895</v>
       </c>
       <c r="E58" t="n">
-        <v>57.78473879584822</v>
+        <v>92.12089327976494</v>
       </c>
       <c r="F58" t="n">
-        <v>10.59446034174881</v>
+        <v>7.06419441405588</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.15286432160804</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59" t="n">
-        <v>0.3008261377135942</v>
+        <v>0.8487528014157127</v>
       </c>
       <c r="C59" t="n">
-        <v>0.3027166186936059</v>
+        <v>0.8534346370757409</v>
       </c>
       <c r="D59" t="n">
-        <v>54.14806055234806</v>
+        <v>76.85964130290601</v>
       </c>
       <c r="E59" t="n">
-        <v>56.43968872284039</v>
+        <v>91.7440491263372</v>
       </c>
       <c r="F59" t="n">
-        <v>9.935305747507153</v>
+        <v>7.094903265823947</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.172914572864322</v>
+        <v>0.59</v>
       </c>
       <c r="B60" t="n">
-        <v>0.2739789561458208</v>
+        <v>0.8283569475144721</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2757712895886922</v>
+        <v>0.8333354530610676</v>
       </c>
       <c r="D60" t="n">
-        <v>50.17330710670818</v>
+        <v>76.30599675359817</v>
       </c>
       <c r="E60" t="n">
-        <v>55.62829507524392</v>
+        <v>90.55628687960355</v>
       </c>
       <c r="F60" t="n">
-        <v>9.366109735297835</v>
+        <v>7.165241176824668</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.192964824120603</v>
+        <v>0.6</v>
       </c>
       <c r="B61" t="n">
-        <v>0.2646575032179602</v>
+        <v>0.8072637561469752</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2660794189274273</v>
+        <v>0.8118046705810043</v>
       </c>
       <c r="D61" t="n">
-        <v>49.29478630542727</v>
+        <v>75.62333810609807</v>
       </c>
       <c r="E61" t="n">
-        <v>54.6540584703058</v>
+        <v>89.17605664816747</v>
       </c>
       <c r="F61" t="n">
-        <v>9.359416155961535</v>
+        <v>7.22149684361712</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.213015075376884</v>
+        <v>0.61</v>
       </c>
       <c r="B62" t="n">
-        <v>0.2703792181861616</v>
+        <v>0.783698613346791</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2718015816638846</v>
+        <v>0.7884239194330808</v>
       </c>
       <c r="D62" t="n">
-        <v>51.20691889732191</v>
+        <v>74.63938500699213</v>
       </c>
       <c r="E62" t="n">
-        <v>53.40613365550243</v>
+        <v>87.0888868751582</v>
       </c>
       <c r="F62" t="n">
-        <v>9.885871822859732</v>
+        <v>7.246328514653158</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.233065326633166</v>
+        <v>0.62</v>
       </c>
       <c r="B63" t="n">
-        <v>0.2701654144527393</v>
+        <v>0.7588108130543534</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2716139643902576</v>
+        <v>0.7633201767784759</v>
       </c>
       <c r="D63" t="n">
-        <v>52.01217034748282</v>
+        <v>73.45381206385093</v>
       </c>
       <c r="E63" t="n">
-        <v>51.79361404511225</v>
+        <v>84.5071860637327</v>
       </c>
       <c r="F63" t="n">
-        <v>10.20730738995307</v>
+        <v>7.248133112921082</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.253115577889447</v>
+        <v>0.63</v>
       </c>
       <c r="B64" t="n">
-        <v>0.2657524611429412</v>
+        <v>0.7337145563609134</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2670780492450642</v>
+        <v>0.7382719115014243</v>
       </c>
       <c r="D64" t="n">
-        <v>51.99451878617801</v>
+        <v>72.17001967928344</v>
       </c>
       <c r="E64" t="n">
-        <v>52.06827220436247</v>
+        <v>81.97535232434699</v>
       </c>
       <c r="F64" t="n">
-        <v>10.36976283054625</v>
+        <v>7.236315686248314</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.273165829145729</v>
+        <v>0.64</v>
       </c>
       <c r="B65" t="n">
-        <v>0.2589520387154308</v>
+        <v>0.7075223520555288</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2600876421485956</v>
+        <v>0.7120170269433882</v>
       </c>
       <c r="D65" t="n">
-        <v>51.4746553561009</v>
+        <v>70.69834992881053</v>
       </c>
       <c r="E65" t="n">
-        <v>52.16935751585148</v>
+        <v>79.0783507686326</v>
       </c>
       <c r="F65" t="n">
-        <v>10.4303421055488</v>
+        <v>7.201274790150874</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.29321608040201</v>
+        <v>0.65</v>
       </c>
       <c r="B66" t="n">
-        <v>0.251089263526077</v>
+        <v>0.6819902042462145</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2520761618682083</v>
+        <v>0.6863798422385017</v>
       </c>
       <c r="D66" t="n">
-        <v>50.69771411218383</v>
+        <v>69.21187780992008</v>
       </c>
       <c r="E66" t="n">
-        <v>51.69121105513064</v>
+        <v>75.92901059460033</v>
       </c>
       <c r="F66" t="n">
-        <v>10.43469131088387</v>
+        <v>7.16001810817868</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.313266331658292</v>
+        <v>0.66</v>
       </c>
       <c r="B67" t="n">
-        <v>0.2431889977585074</v>
+        <v>0.6562283591272137</v>
       </c>
       <c r="C67" t="n">
-        <v>0.244174371957733</v>
+        <v>0.6606529325858638</v>
       </c>
       <c r="D67" t="n">
-        <v>49.86385744364984</v>
+        <v>67.62200900155018</v>
       </c>
       <c r="E67" t="n">
-        <v>50.88873273728236</v>
+        <v>72.6229657185502</v>
       </c>
       <c r="F67" t="n">
-        <v>10.42218587322692</v>
+        <v>7.103168816304894</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.333316582914573</v>
+        <v>0.67</v>
       </c>
       <c r="B68" t="n">
-        <v>0.2357346683114656</v>
+        <v>0.630876345779231</v>
       </c>
       <c r="C68" t="n">
-        <v>0.236799548064094</v>
+        <v>0.6350362767863141</v>
       </c>
       <c r="D68" t="n">
-        <v>49.07336923026826</v>
+        <v>65.99456732821513</v>
       </c>
       <c r="E68" t="n">
-        <v>51.53117560618037</v>
+        <v>69.5247387751391</v>
       </c>
       <c r="F68" t="n">
-        <v>10.41356155761336</v>
+        <v>7.037252277022543</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.353366834170854</v>
+        <v>0.68</v>
       </c>
       <c r="B69" t="n">
-        <v>0.2292159678600833</v>
+        <v>0.6066159129340316</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2303328263728016</v>
+        <v>0.610868056744979</v>
       </c>
       <c r="D69" t="n">
-        <v>48.43391073154469</v>
+        <v>64.40385304849133</v>
       </c>
       <c r="E69" t="n">
-        <v>52.12053933833034</v>
+        <v>68.00091376790076</v>
       </c>
       <c r="F69" t="n">
-        <v>10.43242324213547</v>
+        <v>6.970130265445371</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.373417085427136</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70" t="n">
-        <v>0.2238599558121804</v>
+        <v>0.5819877007119597</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2250175664395478</v>
+        <v>0.5863827144889225</v>
       </c>
       <c r="D70" t="n">
-        <v>48.00295783696177</v>
+        <v>62.69776164086304</v>
       </c>
       <c r="E70" t="n">
-        <v>52.64974986888448</v>
+        <v>67.30144686624571</v>
       </c>
       <c r="F70" t="n">
-        <v>10.49278020958381</v>
+        <v>6.885274493299136</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.393467336683417</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71" t="n">
-        <v>0.219748622069792</v>
+        <v>0.5595207652770189</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2209363767967233</v>
+        <v>0.5634735081069723</v>
       </c>
       <c r="D71" t="n">
-        <v>47.80926782099195</v>
+        <v>61.15097529857829</v>
       </c>
       <c r="E71" t="n">
-        <v>53.11849182060809</v>
+        <v>66.56814343193619</v>
       </c>
       <c r="F71" t="n">
-        <v>10.60300625276428</v>
+        <v>6.812735995561388</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>1.413517587939699</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72" t="n">
-        <v>0.2167283495998769</v>
+        <v>0.5373090588778543</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2179421233978808</v>
+        <v>0.5414192609510957</v>
       </c>
       <c r="D72" t="n">
-        <v>47.83062760791709</v>
+        <v>59.56232616144258</v>
       </c>
       <c r="E72" t="n">
-        <v>53.526986396457</v>
+        <v>65.76983559542214</v>
       </c>
       <c r="F72" t="n">
-        <v>10.76037551983862</v>
+        <v>6.730543427758165</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>1.43356783919598</v>
+        <v>0.72</v>
       </c>
       <c r="B73" t="n">
-        <v>0.2145004846894466</v>
+        <v>0.5153393302718017</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2157292616568079</v>
+        <v>0.5196324530658287</v>
       </c>
       <c r="D73" t="n">
-        <v>48.010437805731</v>
+        <v>57.93152007496175</v>
       </c>
       <c r="E73" t="n">
-        <v>53.8759215850368</v>
+        <v>64.92948568263709</v>
       </c>
       <c r="F73" t="n">
-        <v>10.95403306112416</v>
+        <v>6.638463202145421</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1.453618090452261</v>
+        <v>0.73</v>
       </c>
       <c r="B74" t="n">
-        <v>0.2127270289214878</v>
+        <v>0.4955185672744553</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2139115007396379</v>
+        <v>0.4991652133504643</v>
       </c>
       <c r="D74" t="n">
-        <v>48.27942985033555</v>
+        <v>56.47704058270793</v>
       </c>
       <c r="E74" t="n">
-        <v>54.16638564208728</v>
+        <v>64.24283446460483</v>
       </c>
       <c r="F74" t="n">
-        <v>11.16947045107463</v>
+        <v>6.561678131355866</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>1.473668341708543</v>
+        <v>0.74</v>
       </c>
       <c r="B75" t="n">
-        <v>0.2110773581829597</v>
+        <v>0.476115788668716</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2121425865194277</v>
+        <v>0.4799420351316471</v>
       </c>
       <c r="D75" t="n">
-        <v>48.56579952676418</v>
+        <v>55.0089610171494</v>
       </c>
       <c r="E75" t="n">
-        <v>54.39980467538116</v>
+        <v>63.52998022638813</v>
       </c>
       <c r="F75" t="n">
-        <v>11.39070037781244</v>
+        <v>6.478661564569239</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>1.493718592964824</v>
+        <v>0.75</v>
       </c>
       <c r="B76" t="n">
-        <v>0.2093626486576388</v>
+        <v>0.4633167386231192</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2102402700058611</v>
+        <v>0.4646574178235657</v>
       </c>
       <c r="D76" t="n">
-        <v>48.82667265650252</v>
+        <v>54.25357900115435</v>
       </c>
       <c r="E76" t="n">
-        <v>54.61821000379609</v>
+        <v>62.80435983314523</v>
       </c>
       <c r="F76" t="n">
-        <v>11.60769660832485</v>
+        <v>6.476043958845278</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>1.513768844221105</v>
+        <v>0.76</v>
       </c>
       <c r="B77" t="n">
-        <v>0.2072797658439582</v>
+        <v>0.4544675342785127</v>
       </c>
       <c r="C77" t="n">
-        <v>0.20816187023399</v>
+        <v>0.4558935143684342</v>
       </c>
       <c r="D77" t="n">
-        <v>48.98979373414866</v>
+        <v>53.92691736618289</v>
       </c>
       <c r="E77" t="n">
-        <v>54.79691095405806</v>
+        <v>62.07660721495309</v>
       </c>
       <c r="F77" t="n">
-        <v>11.80280698626432</v>
+        <v>6.522878953047496</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>1.533819095477387</v>
+        <v>0.77</v>
       </c>
       <c r="B78" t="n">
-        <v>0.2046802534511174</v>
+        <v>0.4474851679999746</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2055905820993641</v>
+        <v>0.4486123212553751</v>
       </c>
       <c r="D78" t="n">
-        <v>49.01615327428915</v>
+        <v>53.79705592415048</v>
       </c>
       <c r="E78" t="n">
-        <v>54.9225482351505</v>
+        <v>61.38765932681078</v>
       </c>
       <c r="F78" t="n">
-        <v>11.96557290663436</v>
+        <v>6.592791878072155</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>1.553869346733668</v>
+        <v>0.78</v>
       </c>
       <c r="B79" t="n">
-        <v>0.2013759025793334</v>
+        <v>0.4419267119853268</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2023142564338493</v>
+        <v>0.4432221898022637</v>
       </c>
       <c r="D79" t="n">
-        <v>48.85523857405622</v>
+        <v>53.81879810078747</v>
       </c>
       <c r="E79" t="n">
-        <v>54.99732139632847</v>
+        <v>60.80071092634252</v>
       </c>
       <c r="F79" t="n">
-        <v>12.08219301774231</v>
+        <v>6.681111644223928</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1.57391959798995</v>
+        <v>0.79</v>
       </c>
       <c r="B80" t="n">
-        <v>0.1972069899497516</v>
+        <v>0.437612934342845</v>
       </c>
       <c r="C80" t="n">
-        <v>0.1982564725611732</v>
+        <v>0.4388571291988816</v>
       </c>
       <c r="D80" t="n">
-        <v>48.46118019375969</v>
+        <v>53.97670630513333</v>
       </c>
       <c r="E80" t="n">
-        <v>55.02354306503663</v>
+        <v>60.22063900234579</v>
       </c>
       <c r="F80" t="n">
-        <v>12.13938432812494</v>
+        <v>6.786621100022342</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>1.593969849246231</v>
+        <v>0.8</v>
       </c>
       <c r="B81" t="n">
-        <v>0.1922487073399425</v>
+        <v>0.4342041990788947</v>
       </c>
       <c r="C81" t="n">
-        <v>0.1932857445565519</v>
+        <v>0.4355007919840654</v>
       </c>
       <c r="D81" t="n">
-        <v>47.84457152566463</v>
+        <v>54.2341883578919</v>
       </c>
       <c r="E81" t="n">
-        <v>55.00360410824288</v>
+        <v>59.65177169138614</v>
       </c>
       <c r="F81" t="n">
-        <v>12.13760230418021</v>
+        <v>6.905311329388335</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>1.614020100502513</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82" t="n">
-        <v>0.1865468870428922</v>
+        <v>0.4510575168544065</v>
       </c>
       <c r="C82" t="n">
-        <v>0.1875318595229025</v>
+        <v>0.4532928183739713</v>
       </c>
       <c r="D82" t="n">
-        <v>47.00954895501746</v>
+        <v>57.0434892407409</v>
       </c>
       <c r="E82" t="n">
-        <v>54.93994312985547</v>
+        <v>59.0971359593978</v>
       </c>
       <c r="F82" t="n">
-        <v>12.075778959162</v>
+        <v>7.353790159937343</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>1.634070351758794</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83" t="n">
-        <v>0.1802959489350822</v>
+        <v>0.4781891972405756</v>
       </c>
       <c r="C83" t="n">
-        <v>0.1812204462790503</v>
+        <v>0.480370728805031</v>
       </c>
       <c r="D83" t="n">
-        <v>45.99873177980917</v>
+        <v>61.22132887036136</v>
       </c>
       <c r="E83" t="n">
-        <v>54.83502001481339</v>
+        <v>58.55865491693992</v>
       </c>
       <c r="F83" t="n">
-        <v>11.96290737024777</v>
+        <v>7.989815232145508</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>1.654120603015075</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84" t="n">
-        <v>0.1736640584255199</v>
+        <v>0.5049695421160869</v>
       </c>
       <c r="C84" t="n">
-        <v>0.1744827818210233</v>
+        <v>0.5073024059791506</v>
       </c>
       <c r="D84" t="n">
-        <v>44.85039333138982</v>
+        <v>65.43836130495167</v>
       </c>
       <c r="E84" t="n">
-        <v>54.69129320851899</v>
+        <v>61.45338617810869</v>
       </c>
       <c r="F84" t="n">
-        <v>11.80738049823387</v>
+        <v>8.644316095698668</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>1.674170854271357</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85" t="n">
-        <v>0.1669028740946041</v>
+        <v>0.5290813151200514</v>
       </c>
       <c r="C85" t="n">
-        <v>0.1676192763965783</v>
+        <v>0.5317760902668536</v>
       </c>
       <c r="D85" t="n">
-        <v>43.62673696275095</v>
+        <v>69.38903527377153</v>
       </c>
       <c r="E85" t="n">
-        <v>54.51120041079919</v>
+        <v>64.79069059145687</v>
       </c>
       <c r="F85" t="n">
-        <v>11.62445605520209</v>
+        <v>9.276630686566847</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>1.694221105527638</v>
+        <v>0.85</v>
       </c>
       <c r="B86" t="n">
-        <v>0.160199678666965</v>
+        <v>0.5498269539011728</v>
       </c>
       <c r="C86" t="n">
-        <v>0.1607928567896451</v>
+        <v>0.5521441073734623</v>
       </c>
       <c r="D86" t="n">
-        <v>42.37608853185422</v>
+        <v>72.96827693218134</v>
       </c>
       <c r="E86" t="n">
-        <v>54.29714236446222</v>
+        <v>67.37253233948095</v>
       </c>
       <c r="F86" t="n">
-        <v>11.42644376226466</v>
+        <v>9.871272668256733</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>1.71427135678392</v>
+        <v>0.86</v>
       </c>
       <c r="B87" t="n">
-        <v>0.1551743004979676</v>
+        <v>0.5647729345960083</v>
       </c>
       <c r="C87" t="n">
-        <v>0.156525417798516</v>
+        <v>0.5677659524705519</v>
       </c>
       <c r="D87" t="n">
-        <v>41.5325411523451</v>
+        <v>75.83356382260679</v>
       </c>
       <c r="E87" t="n">
-        <v>54.05146942627944</v>
+        <v>71.48289311818409</v>
       </c>
       <c r="F87" t="n">
-        <v>11.33152090716774</v>
+        <v>10.37958641979263</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>1.734321608040201</v>
+        <v>0.87</v>
       </c>
       <c r="B88" t="n">
-        <v>0.1503857154461869</v>
+        <v>0.574346978803379</v>
       </c>
       <c r="C88" t="n">
-        <v>0.1518985270822401</v>
+        <v>0.5771323957913163</v>
       </c>
       <c r="D88" t="n">
-        <v>40.7216493878675</v>
+        <v>78.01582987520653</v>
       </c>
       <c r="E88" t="n">
-        <v>53.77647062138252</v>
+        <v>75.4469899868854</v>
       </c>
       <c r="F88" t="n">
-        <v>11.24022816384477</v>
+        <v>10.80244631872827</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1.754371859296483</v>
+        <v>0.88</v>
       </c>
       <c r="B89" t="n">
-        <v>0.1451692217614937</v>
+        <v>0.5769749222474913</v>
       </c>
       <c r="C89" t="n">
-        <v>0.146691118341152</v>
+        <v>0.5797953180215176</v>
       </c>
       <c r="D89" t="n">
-        <v>39.76356738300503</v>
+        <v>79.27363057534885</v>
       </c>
       <c r="E89" t="n">
-        <v>53.47436489869087</v>
+        <v>78.35916002313002</v>
       </c>
       <c r="F89" t="n">
-        <v>11.10266214212574</v>
+        <v>11.10277534335867</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1.774422110552764</v>
+        <v>0.89</v>
       </c>
       <c r="B90" t="n">
-        <v>0.1399693137647632</v>
+        <v>0.5726698095536714</v>
       </c>
       <c r="C90" t="n">
-        <v>0.14135423077625</v>
+        <v>0.5759564331486889</v>
       </c>
       <c r="D90" t="n">
-        <v>38.7774202054758</v>
+        <v>79.57624351010156</v>
       </c>
       <c r="E90" t="n">
-        <v>53.1472943239239</v>
+        <v>80.10752302717852</v>
       </c>
       <c r="F90" t="n">
-        <v>10.95105562526824</v>
+        <v>11.27180773151215</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>1.794472361809045</v>
+        <v>0.9</v>
       </c>
       <c r="B91" t="n">
-        <v>0.1399962392044944</v>
+        <v>0.5623265564448235</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1412630375403793</v>
+        <v>0.5652331242554466</v>
       </c>
       <c r="D91" t="n">
-        <v>39.22313312483137</v>
+        <v>79.016946407394</v>
       </c>
       <c r="E91" t="n">
-        <v>52.79731896676459</v>
+        <v>80.69412679787098</v>
       </c>
       <c r="F91" t="n">
-        <v>11.20209334835953</v>
+        <v>11.31834384788772</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>1.814522613065327</v>
+        <v>0.91</v>
       </c>
       <c r="B92" t="n">
-        <v>0.14483976924535</v>
+        <v>0.5457498378597937</v>
       </c>
       <c r="C92" t="n">
-        <v>0.1462114329554406</v>
+        <v>0.5483204236179762</v>
       </c>
       <c r="D92" t="n">
-        <v>41.03357425691028</v>
+        <v>77.53970541010679</v>
       </c>
       <c r="E92" t="n">
-        <v>52.42641325924706</v>
+        <v>80.05231002326001</v>
       </c>
       <c r="F92" t="n">
-        <v>11.85009588989524</v>
+        <v>11.23015293573617</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>1.834572864321608</v>
+        <v>0.92</v>
       </c>
       <c r="B93" t="n">
-        <v>0.1481777272783678</v>
+        <v>0.5235929093173768</v>
       </c>
       <c r="C93" t="n">
-        <v>0.1495127694293694</v>
+        <v>0.5260908227040447</v>
       </c>
       <c r="D93" t="n">
-        <v>42.4430938465788</v>
+        <v>75.20915736436235</v>
       </c>
       <c r="E93" t="n">
-        <v>52.06176663213794</v>
+        <v>78.19067112381926</v>
       </c>
       <c r="F93" t="n">
-        <v>12.39259140738937</v>
+        <v>11.01231642748933</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>1.854623115577889</v>
+        <v>0.93</v>
       </c>
       <c r="B94" t="n">
-        <v>0.1504034083026254</v>
+        <v>0.4964364466377461</v>
       </c>
       <c r="C94" t="n">
-        <v>0.151631238267288</v>
+        <v>0.4990485646897341</v>
       </c>
       <c r="D94" t="n">
-        <v>43.55143660505635</v>
+        <v>72.08348014875278</v>
       </c>
       <c r="E94" t="n">
-        <v>52.81305405977187</v>
+        <v>78.08465187218469</v>
       </c>
       <c r="F94" t="n">
-        <v>12.85518365216249</v>
+        <v>10.66937122827468</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1.874673366834171</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95" t="n">
-        <v>0.1516867124576681</v>
+        <v>0.4947358783607996</v>
       </c>
       <c r="C95" t="n">
-        <v>0.1528039483649071</v>
+        <v>0.4969082551460172</v>
       </c>
       <c r="D95" t="n">
-        <v>44.39788555484294</v>
+        <v>72.60899059436068</v>
       </c>
       <c r="E95" t="n">
-        <v>53.9278695076224</v>
+        <v>77.89345623995922</v>
       </c>
       <c r="F95" t="n">
-        <v>13.24670999251124</v>
+        <v>10.86271498004511</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>1.894723618090452</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96" t="n">
-        <v>0.152060905320346</v>
+        <v>0.4999282796062031</v>
       </c>
       <c r="C96" t="n">
-        <v>0.1531985865707145</v>
+        <v>0.5023457040613073</v>
       </c>
       <c r="D96" t="n">
-        <v>44.98343125268619</v>
+        <v>74.15158671933858</v>
       </c>
       <c r="E96" t="n">
-        <v>56.34669858159762</v>
+        <v>76.81813877321369</v>
       </c>
       <c r="F96" t="n">
-        <v>13.56496195008317</v>
+        <v>11.21151198626557</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>1.914773869346734</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97" t="n">
-        <v>0.151398163979282</v>
+        <v>0.5027007987063296</v>
       </c>
       <c r="C97" t="n">
-        <v>0.1525606723097301</v>
+        <v>0.5051703824542814</v>
       </c>
       <c r="D97" t="n">
-        <v>45.2613225035407</v>
+        <v>75.34769086767308</v>
       </c>
       <c r="E97" t="n">
-        <v>59.46014704422847</v>
+        <v>74.88346569224605</v>
       </c>
       <c r="F97" t="n">
-        <v>13.7931945955542</v>
+        <v>11.51227915406422</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>1.934824120603015</v>
+        <v>0.97</v>
       </c>
       <c r="B98" t="n">
-        <v>0.1488659992940156</v>
+        <v>0.5021014286241487</v>
       </c>
       <c r="C98" t="n">
-        <v>0.1506871527714236</v>
+        <v>0.5052017914786809</v>
       </c>
       <c r="D98" t="n">
-        <v>44.97033771256141</v>
+        <v>76.04178980523344</v>
       </c>
       <c r="E98" t="n">
-        <v>62.2777912793777</v>
+        <v>78.55368729179614</v>
       </c>
       <c r="F98" t="n">
-        <v>13.84802291578193</v>
+        <v>11.73935392718606</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1.954874371859296</v>
+        <v>0.98</v>
       </c>
       <c r="B99" t="n">
-        <v>0.1480619638427745</v>
+        <v>0.4985120603428386</v>
       </c>
       <c r="C99" t="n">
-        <v>0.1486694216049453</v>
+        <v>0.5017914612359768</v>
       </c>
       <c r="D99" t="n">
-        <v>45.19095274911609</v>
+        <v>76.27652235956886</v>
       </c>
       <c r="E99" t="n">
-        <v>64.53850985716849</v>
+        <v>81.9255444718099</v>
       </c>
       <c r="F99" t="n">
-        <v>14.06016710476536</v>
+        <v>11.89698986387716</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>1.974924623115578</v>
+        <v>0.99</v>
       </c>
       <c r="B100" t="n">
-        <v>0.1535890105479046</v>
+        <v>0.491669428362327</v>
       </c>
       <c r="C100" t="n">
-        <v>0.154235653127817</v>
+        <v>0.4950083500366548</v>
       </c>
       <c r="D100" t="n">
-        <v>47.35870367763144</v>
+        <v>75.99719072197027</v>
       </c>
       <c r="E100" t="n">
-        <v>66.1128353522937</v>
+        <v>84.62366204278703</v>
       </c>
       <c r="F100" t="n">
-        <v>14.88574113911858</v>
+        <v>11.9743752788541</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>1.994974874371859</v>
+        <v>1</v>
       </c>
       <c r="B101" t="n">
-        <v>0.1593599303317062</v>
+        <v>0.4814855141767793</v>
       </c>
       <c r="C101" t="n">
-        <v>0.1601246724991503</v>
+        <v>0.4849583294850405</v>
       </c>
       <c r="D101" t="n">
-        <v>49.63702002456555</v>
+        <v>75.17481441581812</v>
       </c>
       <c r="E101" t="n">
-        <v>66.92643090073315</v>
+        <v>86.5753984860047</v>
       </c>
       <c r="F101" t="n">
-        <v>15.76025581714883</v>
+        <v>11.96444331029332</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2.01502512562814</v>
+        <v>1.01</v>
       </c>
       <c r="B102" t="n">
-        <v>0.1652406268140245</v>
+        <v>0.4681720943318245</v>
       </c>
       <c r="C102" t="n">
-        <v>0.1660906210927837</v>
+        <v>0.471777426376193</v>
       </c>
       <c r="D102" t="n">
-        <v>51.98600432017707</v>
+        <v>73.82713864174384</v>
       </c>
       <c r="E102" t="n">
-        <v>66.82443246669135</v>
+        <v>87.614415192541</v>
       </c>
       <c r="F102" t="n">
-        <v>16.6719744468577</v>
+        <v>11.86745358965585</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2.035075376884422</v>
+        <v>1.02</v>
       </c>
       <c r="B103" t="n">
-        <v>0.171114155779631</v>
+        <v>0.4626973120385249</v>
       </c>
       <c r="C103" t="n">
-        <v>0.172024359537642</v>
+        <v>0.4655056701312036</v>
       </c>
       <c r="D103" t="n">
-        <v>54.36952985883372</v>
+        <v>73.68622151617146</v>
       </c>
       <c r="E103" t="n">
-        <v>65.78314295341198</v>
+        <v>87.97008593242916</v>
       </c>
       <c r="F103" t="n">
-        <v>17.60987239100895</v>
+        <v>11.96207691990432</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2.055125628140703</v>
+        <v>1.03</v>
       </c>
       <c r="B104" t="n">
-        <v>0.1768751957897452</v>
+        <v>0.458033638621737</v>
       </c>
       <c r="C104" t="n">
-        <v>0.1778116306058283</v>
+        <v>0.4609359379453826</v>
       </c>
       <c r="D104" t="n">
-        <v>56.75373496199347</v>
+        <v>73.65864714251276</v>
       </c>
       <c r="E104" t="n">
-        <v>63.75003131107066</v>
+        <v>87.69277321037259</v>
       </c>
       <c r="F104" t="n">
-        <v>18.56320472990374</v>
+        <v>12.0748319280184</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2.075175879396985</v>
+        <v>1.04</v>
       </c>
       <c r="B105" t="n">
-        <v>0.1824336397790087</v>
+        <v>0.4513540328923414</v>
       </c>
       <c r="C105" t="n">
-        <v>0.1833767457147986</v>
+        <v>0.4543708670889879</v>
       </c>
       <c r="D105" t="n">
-        <v>59.10836857656952</v>
+        <v>73.28917038176424</v>
       </c>
       <c r="E105" t="n">
-        <v>62.58848066488321</v>
+        <v>86.62840822772189</v>
       </c>
       <c r="F105" t="n">
-        <v>19.52198681780784</v>
+        <v>12.13090709101639</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2.095226130653266</v>
+        <v>1.05</v>
       </c>
       <c r="B106" t="n">
-        <v>0.1877956549541507</v>
+        <v>0.4428223041989794</v>
       </c>
       <c r="C106" t="n">
-        <v>0.1886897510123263</v>
+        <v>0.4458724984660382</v>
       </c>
       <c r="D106" t="n">
-        <v>61.4335455196324</v>
+        <v>72.59520325128008</v>
       </c>
       <c r="E106" t="n">
-        <v>64.97826337635328</v>
+        <v>84.90108864290217</v>
       </c>
       <c r="F106" t="n">
-        <v>20.4859738458342</v>
+        <v>12.13157971431216</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2.115276381909548</v>
+        <v>1.06</v>
       </c>
       <c r="B107" t="n">
-        <v>0.1928677249459675</v>
+        <v>0.4326863575943206</v>
       </c>
       <c r="C107" t="n">
-        <v>0.1937742903409515</v>
+        <v>0.4356029143882527</v>
       </c>
       <c r="D107" t="n">
-        <v>63.69653631394756</v>
+        <v>71.60909854017939</v>
       </c>
       <c r="E107" t="n">
-        <v>67.20607291553075</v>
+        <v>82.82543536618007</v>
       </c>
       <c r="F107" t="n">
-        <v>21.44386521918732</v>
+        <v>12.08075852320563</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2.135326633165829</v>
+        <v>1.07</v>
       </c>
       <c r="B108" t="n">
-        <v>0.1975942461206451</v>
+        <v>0.4212173381340541</v>
       </c>
       <c r="C108" t="n">
-        <v>0.1985689720806499</v>
+        <v>0.4239013574005708</v>
       </c>
       <c r="D108" t="n">
-        <v>65.87608023577488</v>
+        <v>70.36863974295888</v>
       </c>
       <c r="E108" t="n">
-        <v>69.30307939404862</v>
+        <v>80.18205544246032</v>
       </c>
       <c r="F108" t="n">
-        <v>22.3878402018931</v>
+        <v>11.98348303350683</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2.15537688442211</v>
+        <v>1.08</v>
       </c>
       <c r="B109" t="n">
-        <v>0.2019471752148505</v>
+        <v>0.4086753811474283</v>
       </c>
       <c r="C109" t="n">
-        <v>0.2029850430928399</v>
+        <v>0.4111084620625914</v>
       </c>
       <c r="D109" t="n">
-        <v>67.95949494776053</v>
+        <v>68.91144724369687</v>
       </c>
       <c r="E109" t="n">
-        <v>71.18865350457246</v>
+        <v>77.06529376175058</v>
       </c>
       <c r="F109" t="n">
-        <v>23.312749397989</v>
+        <v>11.84500526160678</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2.175427135678392</v>
+        <v>1.09</v>
       </c>
       <c r="B110" t="n">
-        <v>0.2059269470646412</v>
+        <v>0.3953085464302405</v>
       </c>
       <c r="C110" t="n">
-        <v>0.2069878932092174</v>
+        <v>0.3974777984673519</v>
       </c>
       <c r="D110" t="n">
-        <v>69.94341959102154</v>
+        <v>67.27471098606422</v>
       </c>
       <c r="E110" t="n">
-        <v>72.9220760607281</v>
+        <v>73.5716095653686</v>
       </c>
       <c r="F110" t="n">
-        <v>24.21650890458115</v>
+        <v>11.67074205037673</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2.195477386934673</v>
+        <v>1.1</v>
       </c>
       <c r="B111" t="n">
-        <v>0.2095371741091701</v>
+        <v>0.3813188641117232</v>
       </c>
       <c r="C111" t="n">
-        <v>0.2105775365670119</v>
+        <v>0.3832494058376076</v>
       </c>
       <c r="D111" t="n">
-        <v>71.82558797702492</v>
+        <v>65.48926478306707</v>
       </c>
       <c r="E111" t="n">
-        <v>74.56913179778601</v>
+        <v>69.94234611087936</v>
       </c>
       <c r="F111" t="n">
-        <v>25.09737442036866</v>
+        <v>11.46523423064702</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2.215527638190955</v>
+        <v>1.11</v>
       </c>
       <c r="B112" t="n">
-        <v>0.2127750504368302</v>
+        <v>0.3668287888133419</v>
       </c>
       <c r="C112" t="n">
-        <v>0.2138114656984517</v>
+        <v>0.3686491387915766</v>
       </c>
       <c r="D112" t="n">
-        <v>73.60155896366733</v>
+        <v>63.57341330842261</v>
       </c>
       <c r="E112" t="n">
-        <v>76.15821773460661</v>
+        <v>66.14435810545723</v>
       </c>
       <c r="F112" t="n">
-        <v>25.95280580243523</v>
+        <v>11.23100550475809</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2.235577889447236</v>
+        <v>1.12</v>
       </c>
       <c r="B113" t="n">
-        <v>0.2156444802460047</v>
+        <v>0.3519155955228339</v>
       </c>
       <c r="C113" t="n">
-        <v>0.2166806528409759</v>
+        <v>0.3537425427545774</v>
       </c>
       <c r="D113" t="n">
-        <v>75.26919839059033</v>
+        <v>61.53832558002521</v>
       </c>
       <c r="E113" t="n">
-        <v>77.86253864385155</v>
+        <v>62.21069382449059</v>
       </c>
       <c r="F113" t="n">
-        <v>26.7810270510635</v>
+        <v>10.96942415033857</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>2.255628140703517</v>
+        <v>1.13</v>
       </c>
       <c r="B114" t="n">
-        <v>0.2181302403592124</v>
+        <v>0.3366492827305619</v>
       </c>
       <c r="C114" t="n">
-        <v>0.2191819679509745</v>
+        <v>0.3385089813428117</v>
       </c>
       <c r="D114" t="n">
-        <v>76.81968483084009</v>
+        <v>59.39436943852074</v>
       </c>
       <c r="E114" t="n">
-        <v>80.15672874473556</v>
+        <v>58.22406984581438</v>
       </c>
       <c r="F114" t="n">
-        <v>27.57783423424113</v>
+        <v>10.68178546140246</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>2.275678391959799</v>
+        <v>1.14</v>
       </c>
       <c r="B115" t="n">
-        <v>0.2207650207356728</v>
+        <v>0.3210956710420534</v>
       </c>
       <c r="C115" t="n">
-        <v>0.2220893637868676</v>
+        <v>0.3229999538028185</v>
       </c>
       <c r="D115" t="n">
-        <v>78.43868193178778</v>
+        <v>57.15160626296431</v>
       </c>
       <c r="E115" t="n">
-        <v>82.22450681461213</v>
+        <v>57.40744995548883</v>
       </c>
       <c r="F115" t="n">
-        <v>28.40935048692732</v>
+        <v>10.36939513232744</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>2.29572864321608</v>
+        <v>1.15</v>
       </c>
       <c r="B116" t="n">
-        <v>0.2248733256424129</v>
+        <v>0.3053158667814663</v>
       </c>
       <c r="C116" t="n">
-        <v>0.2261396318812126</v>
+        <v>0.3072717516923317</v>
       </c>
       <c r="D116" t="n">
-        <v>80.602337103312</v>
+        <v>54.81966204560747</v>
       </c>
       <c r="E116" t="n">
-        <v>84.02673156656829</v>
+        <v>56.67860486719904</v>
       </c>
       <c r="F116" t="n">
-        <v>29.45020478495061</v>
+        <v>10.03354322216343</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>2.315778894472362</v>
+        <v>1.16</v>
       </c>
       <c r="B117" t="n">
-        <v>0.2285940954806516</v>
+        <v>0.289397244732352</v>
       </c>
       <c r="C117" t="n">
-        <v>0.229796253821159</v>
+        <v>0.2913758774320674</v>
       </c>
       <c r="D117" t="n">
-        <v>82.65159502284642</v>
+        <v>52.41330193450151</v>
       </c>
       <c r="E117" t="n">
-        <v>85.59187100362389</v>
+        <v>55.95891880913215</v>
       </c>
       <c r="F117" t="n">
-        <v>30.46270482102048</v>
+        <v>9.676529860506944</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>2.335829145728643</v>
+        <v>1.17</v>
       </c>
       <c r="B118" t="n">
-        <v>0.2319056685652923</v>
+        <v>0.2765571436365498</v>
       </c>
       <c r="C118" t="n">
-        <v>0.2330910364652987</v>
+        <v>0.2783861541232416</v>
       </c>
       <c r="D118" t="n">
-        <v>84.57491627902304</v>
+        <v>50.51959750240263</v>
       </c>
       <c r="E118" t="n">
-        <v>86.84968278075499</v>
+        <v>55.7247700310613</v>
       </c>
       <c r="F118" t="n">
-        <v>31.44146555989128</v>
+        <v>9.407319088658808</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>2.355879396984924</v>
+        <v>1.18</v>
       </c>
       <c r="B119" t="n">
-        <v>0.2348371608806562</v>
+        <v>0.2677042716803085</v>
       </c>
       <c r="C119" t="n">
-        <v>0.2360646837386907</v>
+        <v>0.2696728630536773</v>
       </c>
       <c r="D119" t="n">
-        <v>86.37916755290776</v>
+        <v>49.3203837960328</v>
       </c>
       <c r="E119" t="n">
-        <v>87.88123620477533</v>
+        <v>55.3438445321617</v>
       </c>
       <c r="F119" t="n">
-        <v>32.38785603443411</v>
+        <v>9.262507794067083</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>2.375929648241206</v>
+        <v>1.19</v>
       </c>
       <c r="B120" t="n">
-        <v>0.2373192963225347</v>
+        <v>0.2632811157144266</v>
       </c>
       <c r="C120" t="n">
-        <v>0.2386845855614264</v>
+        <v>0.2646575238087207</v>
       </c>
       <c r="D120" t="n">
-        <v>88.03508094978169</v>
+        <v>48.91654895529882</v>
       </c>
       <c r="E120" t="n">
-        <v>88.61189853609093</v>
+        <v>54.82992772062232</v>
       </c>
       <c r="F120" t="n">
-        <v>33.28966896374914</v>
+        <v>9.26451957262667</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>2.395979899497487</v>
+        <v>1.2</v>
       </c>
       <c r="B121" t="n">
-        <v>0.2393434006885685</v>
+        <v>0.2673797997194608</v>
       </c>
       <c r="C121" t="n">
-        <v>0.2408462294251549</v>
+        <v>0.2687881372715153</v>
       </c>
       <c r="D121" t="n">
-        <v>89.53519147667686</v>
+        <v>50.09553034669916</v>
       </c>
       <c r="E121" t="n">
-        <v>89.06442387960102</v>
+        <v>54.25635751723059</v>
       </c>
       <c r="F121" t="n">
-        <v>34.14263762532143</v>
+        <v>9.567541537784665</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>2.416030150753769</v>
+        <v>1.21</v>
       </c>
       <c r="B122" t="n">
-        <v>0.240903783413692</v>
+        <v>0.2698958622616016</v>
       </c>
       <c r="C122" t="n">
-        <v>0.24253167199232</v>
+        <v>0.2713348437907711</v>
       </c>
       <c r="D122" t="n">
-        <v>90.8730510027613</v>
+        <v>50.98832388359907</v>
       </c>
       <c r="E122" t="n">
-        <v>89.35596892152299</v>
+        <v>53.61846578077204</v>
       </c>
       <c r="F122" t="n">
-        <v>34.942791017604</v>
+        <v>9.819202981114859</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>2.43608040201005</v>
+        <v>1.22</v>
       </c>
       <c r="B123" t="n">
-        <v>0.2419974264081023</v>
+        <v>0.2708895448517799</v>
       </c>
       <c r="C123" t="n">
-        <v>0.2437367724624461</v>
+        <v>0.2723430869797882</v>
       </c>
       <c r="D123" t="n">
-        <v>92.04315661045878</v>
+        <v>51.59899146998701</v>
       </c>
       <c r="E123" t="n">
-        <v>90.31943575161442</v>
+        <v>52.88185833801776</v>
       </c>
       <c r="F123" t="n">
-        <v>35.68644230525344</v>
+        <v>10.01892615222607</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>2.456130653266332</v>
+        <v>1.23</v>
       </c>
       <c r="B124" t="n">
-        <v>0.2426236894566771</v>
+        <v>0.2705389962156297</v>
       </c>
       <c r="C124" t="n">
-        <v>0.2444909858207242</v>
+        <v>0.2719980608449019</v>
       </c>
       <c r="D124" t="n">
-        <v>93.04087945302868</v>
+        <v>51.95461426716997</v>
       </c>
       <c r="E124" t="n">
-        <v>91.03284152571514</v>
+        <v>52.06034181036117</v>
       </c>
       <c r="F124" t="n">
-        <v>36.37017609051233</v>
+        <v>10.17066542277496</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>2.476180904522613</v>
+        <v>1.24</v>
       </c>
       <c r="B125" t="n">
-        <v>0.2427913381594626</v>
+        <v>0.2690633770458431</v>
       </c>
       <c r="C125" t="n">
-        <v>0.2447795518106334</v>
+        <v>0.2704933107430204</v>
       </c>
       <c r="D125" t="n">
-        <v>93.8652190360668</v>
+        <v>52.09132603484592</v>
       </c>
       <c r="E125" t="n">
-        <v>91.46544306758983</v>
+        <v>51.4629275417388</v>
       </c>
       <c r="F125" t="n">
-        <v>36.9919478119409</v>
+        <v>10.28033411801501</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>2.496231155778894</v>
+        <v>1.25</v>
       </c>
       <c r="B126" t="n">
-        <v>0.242524866573737</v>
+        <v>0.2666867048119054</v>
       </c>
       <c r="C126" t="n">
-        <v>0.244601067130319</v>
+        <v>0.2680513332203368</v>
       </c>
       <c r="D126" t="n">
-        <v>94.52141462102031</v>
+        <v>52.04757711059691</v>
       </c>
       <c r="E126" t="n">
-        <v>91.62578160618497</v>
+        <v>51.965942804279</v>
       </c>
       <c r="F126" t="n">
-        <v>37.55217911457688</v>
+        <v>10.35453646638511</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>2.516281407035176</v>
+        <v>1.26</v>
       </c>
       <c r="B127" t="n">
-        <v>0.2418560243055793</v>
+        <v>0.2636232522460854</v>
       </c>
       <c r="C127" t="n">
-        <v>0.243959290550847</v>
+        <v>0.2649122102251783</v>
       </c>
       <c r="D127" t="n">
-        <v>95.01786266461629</v>
+        <v>51.86129984085518</v>
       </c>
       <c r="E127" t="n">
-        <v>91.55954782412078</v>
+        <v>52.19977721082558</v>
       </c>
       <c r="F127" t="n">
-        <v>38.05262290863738</v>
+        <v>10.40001760330221</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>2.536331658291457</v>
+        <v>1.27</v>
       </c>
       <c r="B128" t="n">
-        <v>0.2408161289231908</v>
+        <v>0.2600737568066124</v>
       </c>
       <c r="C128" t="n">
-        <v>0.2428593946447906</v>
+        <v>0.2612847099317679</v>
       </c>
       <c r="D128" t="n">
-        <v>95.36318610080322</v>
+        <v>51.56908089634242</v>
       </c>
       <c r="E128" t="n">
-        <v>91.79205582062991</v>
+        <v>52.18668906459144</v>
       </c>
       <c r="F128" t="n">
-        <v>38.49523070195418</v>
+        <v>10.42349215190558</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>2.556381909547738</v>
+        <v>1.28</v>
       </c>
       <c r="B129" t="n">
-        <v>0.2394359584191643</v>
+        <v>0.2563025363656052</v>
       </c>
       <c r="C129" t="n">
-        <v>0.2413703918984174</v>
+        <v>0.2573574734105122</v>
       </c>
       <c r="D129" t="n">
-        <v>95.5661846567678</v>
+        <v>51.22146699951921</v>
       </c>
       <c r="E129" t="n">
-        <v>92.37151960340474</v>
+        <v>52.0740292675686</v>
       </c>
       <c r="F129" t="n">
-        <v>38.88213599906121</v>
+        <v>10.4347515717016</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>2.57643216080402</v>
+        <v>1.29</v>
       </c>
       <c r="B130" t="n">
-        <v>0.2377456565621622</v>
+        <v>0.2523740790852702</v>
       </c>
       <c r="C130" t="n">
-        <v>0.239573470955606</v>
+        <v>0.25335753806904</v>
       </c>
       <c r="D130" t="n">
-        <v>95.63578833399841</v>
+        <v>50.83040810155277</v>
       </c>
       <c r="E130" t="n">
-        <v>92.61244819539056</v>
+        <v>51.80434702010794</v>
       </c>
       <c r="F130" t="n">
-        <v>39.21563804683706</v>
+        <v>10.43598481427518</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>2.596482412060301</v>
+        <v>1.3</v>
       </c>
       <c r="B131" t="n">
-        <v>0.2358396214698062</v>
+        <v>0.2484025186869171</v>
       </c>
       <c r="C131" t="n">
-        <v>0.2374992648678809</v>
+        <v>0.2493563993522889</v>
       </c>
       <c r="D131" t="n">
-        <v>95.60735275017858</v>
+        <v>50.41833347162985</v>
       </c>
       <c r="E131" t="n">
-        <v>92.84944982101293</v>
+        <v>51.42018448654988</v>
       </c>
       <c r="F131" t="n">
-        <v>39.50907027934143</v>
+        <v>10.43162509280509</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>2.616532663316583</v>
+        <v>1.31</v>
       </c>
       <c r="B132" t="n">
-        <v>0.233696426412065</v>
+        <v>0.2444620275247843</v>
       </c>
       <c r="C132" t="n">
-        <v>0.2351960901654274</v>
+        <v>0.2454409158840712</v>
       </c>
       <c r="D132" t="n">
-        <v>95.4700985812004</v>
+        <v>50.00021180871344</v>
       </c>
       <c r="E132" t="n">
-        <v>94.57876997571027</v>
+        <v>51.02614720570452</v>
       </c>
       <c r="F132" t="n">
-        <v>39.75700526010687</v>
+        <v>10.42469293314803</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>2.636582914572864</v>
+        <v>1.32</v>
       </c>
       <c r="B133" t="n">
-        <v>0.231422737845479</v>
+        <v>0.2406040355845795</v>
       </c>
       <c r="C133" t="n">
-        <v>0.2327447000642972</v>
+        <v>0.241626173756208</v>
       </c>
       <c r="D133" t="n">
-        <v>95.26570805842736</v>
+        <v>49.58678799480435</v>
       </c>
       <c r="E133" t="n">
-        <v>96.12854735639048</v>
+        <v>51.10692693359783</v>
       </c>
       <c r="F133" t="n">
-        <v>39.97589215211044</v>
+        <v>10.41741679627832</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>2.656633165829146</v>
+        <v>1.33</v>
       </c>
       <c r="B134" t="n">
-        <v>0.2289839056966894</v>
+        <v>0.2368765500441971</v>
       </c>
       <c r="C134" t="n">
-        <v>0.2302087053519369</v>
+        <v>0.237923071690594</v>
       </c>
       <c r="D134" t="n">
-        <v>94.97858341135162</v>
+        <v>49.18841734398837</v>
       </c>
       <c r="E134" t="n">
-        <v>97.49894663805902</v>
+        <v>51.4279436214285</v>
       </c>
       <c r="F134" t="n">
-        <v>40.1584932479622</v>
+        <v>10.41201108500661</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>2.676683417085427</v>
+        <v>1.34</v>
       </c>
       <c r="B135" t="n">
-        <v>0.2263880854662738</v>
+        <v>0.23345157757473</v>
       </c>
       <c r="C135" t="n">
-        <v>0.2276196362197443</v>
+        <v>0.2345342240614171</v>
       </c>
       <c r="D135" t="n">
-        <v>94.61058200278705</v>
+        <v>48.84169760748937</v>
       </c>
       <c r="E135" t="n">
-        <v>98.69106936197248</v>
+        <v>51.73427016159471</v>
       </c>
       <c r="F135" t="n">
-        <v>40.30480776021188</v>
+        <v>10.41635278833025</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>2.696733668341708</v>
+        <v>1.35</v>
       </c>
       <c r="B136" t="n">
-        <v>0.2236422702400037</v>
+        <v>0.2302229526397858</v>
       </c>
       <c r="C136" t="n">
-        <v>0.2249266308176701</v>
+        <v>0.231329782751052</v>
       </c>
       <c r="D136" t="n">
-        <v>94.16317389015232</v>
+        <v>48.52566849812724</v>
       </c>
       <c r="E136" t="n">
-        <v>99.70686491804507</v>
+        <v>52.02575872892958</v>
       </c>
       <c r="F136" t="n">
-        <v>40.41469237861374</v>
+        <v>10.42618501122609</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>2.71678391959799</v>
+        <v>1.36</v>
       </c>
       <c r="B137" t="n">
-        <v>0.2207392965776596</v>
+        <v>0.2272774682737869</v>
       </c>
       <c r="C137" t="n">
-        <v>0.2220543959176753</v>
+        <v>0.2284157917353218</v>
       </c>
       <c r="D137" t="n">
-        <v>93.63191186441267</v>
+        <v>48.25967916713694</v>
       </c>
       <c r="E137" t="n">
-        <v>100.5490439382796</v>
+        <v>52.30230214118301</v>
       </c>
       <c r="F137" t="n">
-        <v>40.48546399288649</v>
+        <v>10.44584242841118</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>2.736834170854271</v>
+        <v>1.37</v>
       </c>
       <c r="B138" t="n">
-        <v>0.2176919920330498</v>
+        <v>0.224678418651281</v>
       </c>
       <c r="C138" t="n">
-        <v>0.2190081865596115</v>
+        <v>0.2258239815838742</v>
       </c>
       <c r="D138" t="n">
-        <v>93.02080126169531</v>
+        <v>48.0585944154347</v>
       </c>
       <c r="E138" t="n">
-        <v>101.2907059244357</v>
+        <v>52.56383161594489</v>
       </c>
       <c r="F138" t="n">
-        <v>40.51806449228052</v>
+        <v>10.47880511719304</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>2.756884422110553</v>
+        <v>1.38</v>
       </c>
       <c r="B139" t="n">
-        <v>0.2145234785137942</v>
+        <v>0.222345118701671</v>
       </c>
       <c r="C139" t="n">
-        <v>0.2158499924695595</v>
+        <v>0.2235276919837422</v>
       </c>
       <c r="D139" t="n">
-        <v>92.33843909441188</v>
+        <v>47.90665245094685</v>
       </c>
       <c r="E139" t="n">
-        <v>101.8701234404129</v>
+        <v>52.81031453088888</v>
       </c>
       <c r="F139" t="n">
-        <v>40.51550158969585</v>
+        <v>10.52192115148405</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>2.776934673366834</v>
+        <v>1.39</v>
       </c>
       <c r="B140" t="n">
-        <v>0.2112787260873986</v>
+        <v>0.2203667339075292</v>
       </c>
       <c r="C140" t="n">
-        <v>0.2125363548020907</v>
+        <v>0.2215401164275704</v>
       </c>
       <c r="D140" t="n">
-        <v>91.60318451456104</v>
+        <v>47.82444890581343</v>
       </c>
       <c r="E140" t="n">
-        <v>103.2054146482725</v>
+        <v>53.04175220151301</v>
       </c>
       <c r="F140" t="n">
-        <v>40.48520723694673</v>
+        <v>10.57998144716833</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>2.796984924623116</v>
+        <v>1.4</v>
       </c>
       <c r="B141" t="n">
-        <v>0.207991599636627</v>
+        <v>0.2186376875007054</v>
       </c>
       <c r="C141" t="n">
-        <v>0.2091079634414897</v>
+        <v>0.2198544691920769</v>
       </c>
       <c r="D141" t="n">
-        <v>90.82911019284614</v>
+        <v>47.79056884894869</v>
       </c>
       <c r="E141" t="n">
-        <v>104.4169282820728</v>
+        <v>53.25817768840436</v>
       </c>
       <c r="F141" t="n">
-        <v>40.43293958496348</v>
+        <v>10.64854737167723</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>2.817035175879397</v>
+        <v>1.41</v>
       </c>
       <c r="B142" t="n">
-        <v>0.2047017428982891</v>
+        <v>0.2171750792555133</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2056831743518743</v>
+        <v>0.2183716085492117</v>
       </c>
       <c r="D142" t="n">
-        <v>90.03325454464024</v>
+        <v>47.80994458873637</v>
       </c>
       <c r="E142" t="n">
-        <v>105.4628368896669</v>
+        <v>53.45965364450777</v>
       </c>
       <c r="F142" t="n">
-        <v>40.36596609069355</v>
+        <v>10.72895650444828</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>2.837085427135678</v>
+        <v>1.42</v>
       </c>
       <c r="B143" t="n">
-        <v>0.2014143353282849</v>
+        <v>0.2159341113350371</v>
       </c>
       <c r="C143" t="n">
-        <v>0.2023255916136842</v>
+        <v>0.217181845755144</v>
       </c>
       <c r="D143" t="n">
-        <v>89.21788620488444</v>
+        <v>47.87389215279371</v>
       </c>
       <c r="E143" t="n">
-        <v>106.3462655735771</v>
+        <v>53.64627021115284</v>
       </c>
       <c r="F143" t="n">
-        <v>40.28510260591813</v>
+        <v>10.81950054525489</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>2.857135678391959</v>
+        <v>1.43</v>
       </c>
       <c r="B144" t="n">
-        <v>0.1981284569952071</v>
+        <v>0.2148323061811713</v>
       </c>
       <c r="C144" t="n">
-        <v>0.1990394829999899</v>
+        <v>0.2160625972397839</v>
       </c>
       <c r="D144" t="n">
-        <v>88.38261780483749</v>
+        <v>47.96503514479566</v>
       </c>
       <c r="E144" t="n">
-        <v>107.0708528206011</v>
+        <v>53.81814297017411</v>
       </c>
       <c r="F144" t="n">
-        <v>40.18998618285763</v>
+        <v>10.91643758758512</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>2.877185929648241</v>
+        <v>1.44</v>
       </c>
       <c r="B145" t="n">
-        <v>0.1948534233066864</v>
+        <v>0.2138982895555688</v>
       </c>
       <c r="C145" t="n">
-        <v>0.1957545749439746</v>
+        <v>0.2151668409140113</v>
       </c>
       <c r="D145" t="n">
-        <v>87.531648354155</v>
+        <v>48.09046128442355</v>
       </c>
       <c r="E145" t="n">
-        <v>107.6406862531952</v>
+        <v>53.97541095828964</v>
       </c>
       <c r="F145" t="n">
-        <v>40.08234911609525</v>
+        <v>11.02152186573901</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>2.897236180904522</v>
+        <v>1.45</v>
       </c>
       <c r="B146" t="n">
-        <v>0.1915993894753808</v>
+        <v>0.2130150255534223</v>
       </c>
       <c r="C146" t="n">
-        <v>0.1924716085304535</v>
+        <v>0.2142582917474483</v>
       </c>
       <c r="D146" t="n">
-        <v>86.6696733931943</v>
+        <v>48.22446072889716</v>
       </c>
       <c r="E146" t="n">
-        <v>108.0945232977399</v>
+        <v>54.11823474845564</v>
       </c>
       <c r="F146" t="n">
-        <v>39.96420625299942</v>
+        <v>11.12898388927021</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>2.917286432160804</v>
+        <v>1.46</v>
       </c>
       <c r="B147" t="n">
-        <v>0.1883413882495037</v>
+        <v>0.2121803376159712</v>
       </c>
       <c r="C147" t="n">
-        <v>0.1892268369883509</v>
+        <v>0.2134113340536946</v>
       </c>
       <c r="D147" t="n">
-        <v>85.78551808493783</v>
+        <v>48.36677505064151</v>
       </c>
       <c r="E147" t="n">
-        <v>108.4374634171294</v>
+        <v>54.24679460210521</v>
       </c>
       <c r="F147" t="n">
-        <v>39.83026375158943</v>
+        <v>11.23880454285609</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>2.937336683417085</v>
+        <v>1.47</v>
       </c>
       <c r="B148" t="n">
-        <v>0.1850395428235925</v>
+        <v>0.2113957496540088</v>
       </c>
       <c r="C148" t="n">
-        <v>0.1860053787127165</v>
+        <v>0.21250548120904</v>
       </c>
       <c r="D148" t="n">
-        <v>84.86085729571721</v>
+        <v>48.51798153322287</v>
       </c>
       <c r="E148" t="n">
-        <v>108.6385737543221</v>
+        <v>54.36128869505767</v>
       </c>
       <c r="F148" t="n">
-        <v>39.67174242594849</v>
+        <v>11.35115858708496</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2.957386934673367</v>
+        <v>1.48</v>
       </c>
       <c r="B149" t="n">
-        <v>0.181709529499976</v>
+        <v>0.210570084752978</v>
       </c>
       <c r="C149" t="n">
-        <v>0.182747046726623</v>
+        <v>0.211576970346063</v>
       </c>
       <c r="D149" t="n">
-        <v>83.90251763957365</v>
+        <v>48.65724623811666</v>
       </c>
       <c r="E149" t="n">
-        <v>108.7030498614336</v>
+        <v>54.4643040437721</v>
       </c>
       <c r="F149" t="n">
-        <v>39.49146767483435</v>
+        <v>11.46118105893298</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2.977437185929648</v>
+        <v>1.49</v>
       </c>
       <c r="B150" t="n">
-        <v>0.1782970446626725</v>
+        <v>0.2096836773648297</v>
       </c>
       <c r="C150" t="n">
-        <v>0.179408274364388</v>
+        <v>0.2106221090506606</v>
       </c>
       <c r="D150" t="n">
-        <v>82.88499044544183</v>
+        <v>48.779801865334</v>
       </c>
       <c r="E150" t="n">
-        <v>108.636283375965</v>
+        <v>54.57906730700252</v>
       </c>
       <c r="F150" t="n">
-        <v>39.27702918863292</v>
+        <v>11.56768441896763</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>2.99748743718593</v>
+        <v>1.5</v>
       </c>
       <c r="B151" t="n">
-        <v>0.1748595881215708</v>
+        <v>0.2087255135517735</v>
       </c>
       <c r="C151" t="n">
-        <v>0.1759851000356167</v>
+        <v>0.2096609812803241</v>
       </c>
       <c r="D151" t="n">
-        <v>81.83441114234286</v>
+        <v>48.88278447565067</v>
       </c>
       <c r="E151" t="n">
-        <v>108.4438185747261</v>
+        <v>54.68002926927063</v>
       </c>
       <c r="F151" t="n">
-        <v>39.04032864483363</v>
+        <v>11.66990517209335</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>3.017537688442211</v>
+        <v>1.51</v>
       </c>
       <c r="B152" t="n">
-        <v>0.1713898611028995</v>
+        <v>0.2077017739040008</v>
       </c>
       <c r="C152" t="n">
-        <v>0.1724910604284881</v>
+        <v>0.2085956515513017</v>
       </c>
       <c r="D152" t="n">
-        <v>80.74710653122732</v>
+        <v>48.96731508939747</v>
       </c>
       <c r="E152" t="n">
-        <v>108.1313123883593</v>
+        <v>54.7674344993347</v>
       </c>
       <c r="F152" t="n">
-        <v>38.77928554999283</v>
+        <v>11.76801927208811</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>3.037587939698492</v>
+        <v>1.52</v>
       </c>
       <c r="B153" t="n">
-        <v>0.1679416427061382</v>
+        <v>0.2065504287376519</v>
       </c>
       <c r="C153" t="n">
-        <v>0.1689359820891131</v>
+        <v>0.2074164899491825</v>
       </c>
       <c r="D153" t="n">
-        <v>79.64827891114209</v>
+        <v>49.01836572404699</v>
       </c>
       <c r="E153" t="n">
-        <v>107.7044977735036</v>
+        <v>54.841538810321</v>
       </c>
       <c r="F153" t="n">
-        <v>38.50573230138091</v>
+        <v>11.85830311504798</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>3.057638190954774</v>
+        <v>1.53</v>
       </c>
       <c r="B154" t="n">
-        <v>0.1645594847234945</v>
+        <v>0.205244048664261</v>
       </c>
       <c r="C154" t="n">
-        <v>0.1653774308510715</v>
+        <v>0.206112835662138</v>
       </c>
       <c r="D154" t="n">
-        <v>78.55939895200255</v>
+        <v>49.02878634020916</v>
       </c>
       <c r="E154" t="n">
-        <v>107.1818072398533</v>
+        <v>54.90260790556197</v>
       </c>
       <c r="F154" t="n">
-        <v>38.23000703474715</v>
+        <v>11.93885576075625</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>3.077688442211055</v>
+        <v>1.54</v>
       </c>
       <c r="B155" t="n">
-        <v>0.1612645956378606</v>
+        <v>0.2037533855217089</v>
       </c>
       <c r="C155" t="n">
-        <v>0.1619387715366936</v>
+        <v>0.2046400741864561</v>
       </c>
       <c r="D155" t="n">
-        <v>77.49127820814238</v>
+        <v>48.99081828628113</v>
       </c>
       <c r="E155" t="n">
-        <v>106.5992465965086</v>
+        <v>54.95091609862173</v>
       </c>
       <c r="F155" t="n">
-        <v>37.95750079833585</v>
+        <v>12.00758158042283</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>3.097738693467337</v>
+        <v>1.55</v>
       </c>
       <c r="B156" t="n">
-        <v>0.1579941683104512</v>
+        <v>0.2020536418926428</v>
       </c>
       <c r="C156" t="n">
-        <v>0.1587182497738229</v>
+        <v>0.2030191753837971</v>
       </c>
       <c r="D156" t="n">
-        <v>76.41435939300086</v>
+        <v>48.89759734267163</v>
       </c>
       <c r="E156" t="n">
-        <v>105.9177258187539</v>
+        <v>54.98674510629418</v>
       </c>
       <c r="F156" t="n">
-        <v>37.67383998013483</v>
+        <v>12.06255619972514</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>3.117788944723618</v>
+        <v>1.56</v>
       </c>
       <c r="B157" t="n">
-        <v>0.1559526250602893</v>
+        <v>0.2001789207741098</v>
       </c>
       <c r="C157" t="n">
-        <v>0.1568531101120852</v>
+        <v>0.2011866125292182</v>
       </c>
       <c r="D157" t="n">
-        <v>75.91516515239486</v>
+        <v>48.75645046562858</v>
       </c>
       <c r="E157" t="n">
-        <v>105.1429531448953</v>
+        <v>55.01038291300154</v>
       </c>
       <c r="F157" t="n">
-        <v>37.6699796484674</v>
+        <v>12.10533495478309</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>3.137839195979899</v>
+        <v>1.57</v>
       </c>
       <c r="B158" t="n">
-        <v>0.1551144432730137</v>
+        <v>0.1981057680396816</v>
       </c>
       <c r="C158" t="n">
-        <v>0.1561382526427489</v>
+        <v>0.1991107980664425</v>
       </c>
       <c r="D158" t="n">
-        <v>75.99273253961462</v>
+        <v>48.56080886441943</v>
       </c>
       <c r="E158" t="n">
-        <v>104.2805842305616</v>
+        <v>55.02212270485651</v>
       </c>
       <c r="F158" t="n">
-        <v>37.95096962999764</v>
+        <v>12.13404765096154</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>3.157889447236181</v>
+        <v>1.58</v>
       </c>
       <c r="B159" t="n">
-        <v>0.1542058722193027</v>
+        <v>0.1957970876943698</v>
       </c>
       <c r="C159" t="n">
-        <v>0.1553136502784562</v>
+        <v>0.196815614771174</v>
       </c>
       <c r="D159" t="n">
-        <v>76.03034709198216</v>
+        <v>48.30059200032523</v>
       </c>
       <c r="E159" t="n">
-        <v>103.3362021214096</v>
+        <v>55.02226187134325</v>
       </c>
       <c r="F159" t="n">
-        <v>38.21237461787503</v>
+        <v>12.14589919436426</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>3.177939698492462</v>
+        <v>1.59</v>
       </c>
       <c r="B160" t="n">
-        <v>0.1532185203682506</v>
+        <v>0.1932645475976983</v>
       </c>
       <c r="C160" t="n">
-        <v>0.1544303002828027</v>
+        <v>0.194349406412951</v>
       </c>
       <c r="D160" t="n">
-        <v>76.02318408892005</v>
+        <v>47.97759320466874</v>
       </c>
       <c r="E160" t="n">
-        <v>102.3152995942703</v>
+        <v>55.01110107256134</v>
       </c>
       <c r="F160" t="n">
-        <v>38.4513718616439</v>
+        <v>12.1410350747185</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>3.197989949748743</v>
+        <v>1.6</v>
       </c>
       <c r="B161" t="n">
-        <v>0.1521390738520023</v>
+        <v>0.190600200474211</v>
       </c>
       <c r="C161" t="n">
-        <v>0.1534354807296675</v>
+        <v>0.1916296656057858</v>
       </c>
       <c r="D161" t="n">
-        <v>75.96385598299693</v>
+        <v>47.61375958822581</v>
       </c>
       <c r="E161" t="n">
-        <v>101.2232637153837</v>
+        <v>54.98894336970019</v>
       </c>
       <c r="F161" t="n">
-        <v>38.66377260912474</v>
+        <v>12.12474431624842</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>3.218040201005025</v>
+        <v>1.61</v>
       </c>
       <c r="B162" t="n">
-        <v>0.1509967591363455</v>
+        <v>0.1877519893013185</v>
       </c>
       <c r="C162" t="n">
-        <v>0.1523739417400657</v>
+        <v>0.1887418696332996</v>
       </c>
       <c r="D162" t="n">
-        <v>75.86618230027727</v>
+        <v>47.19538815504169</v>
       </c>
       <c r="E162" t="n">
-        <v>100.065362462052</v>
+        <v>54.95609341643524</v>
       </c>
       <c r="F162" t="n">
-        <v>38.85615537394656</v>
+        <v>12.09332069878507</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>3.238090452261306</v>
+        <v>1.62</v>
       </c>
       <c r="B163" t="n">
-        <v>0.1497913094429703</v>
+        <v>0.1847349229290301</v>
       </c>
       <c r="C163" t="n">
-        <v>0.1512142280341514</v>
+        <v>0.1857146377554794</v>
       </c>
       <c r="D163" t="n">
-        <v>75.7294377464013</v>
+        <v>46.72541392051642</v>
       </c>
       <c r="E163" t="n">
-        <v>98.8467332613793</v>
+        <v>54.91285670879543</v>
       </c>
       <c r="F163" t="n">
-        <v>39.02777927646598</v>
+        <v>12.04726056141338</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>3.258140703517588</v>
+        <v>1.63</v>
       </c>
       <c r="B164" t="n">
-        <v>0.148517700014124</v>
+        <v>0.1815785033929711</v>
       </c>
       <c r="C164" t="n">
-        <v>0.1499968736464064</v>
+        <v>0.1825365666553441</v>
       </c>
       <c r="D164" t="n">
-        <v>75.55047331770447</v>
+        <v>46.21055405586876</v>
       </c>
       <c r="E164" t="n">
-        <v>97.57237330003224</v>
+        <v>54.85953889109463</v>
       </c>
       <c r="F164" t="n">
-        <v>39.17663736658544</v>
+        <v>11.988060104641</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>3.278190954773869</v>
+        <v>1.64</v>
       </c>
       <c r="B165" t="n">
-        <v>0.1471876178649957</v>
+        <v>0.1783641380303509</v>
       </c>
       <c r="C165" t="n">
-        <v>0.1486772745246421</v>
+        <v>0.1792372430664693</v>
       </c>
       <c r="D165" t="n">
-        <v>75.3346306316344</v>
+        <v>45.6710005832314</v>
       </c>
       <c r="E165" t="n">
-        <v>96.24713146604496</v>
+        <v>54.79644511537612</v>
       </c>
       <c r="F165" t="n">
-        <v>39.30511239827034</v>
+        <v>11.92077541798955</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>3.298241206030151</v>
+        <v>1.65</v>
       </c>
       <c r="B166" t="n">
-        <v>0.1458264643988337</v>
+        <v>0.1750554922016589</v>
       </c>
       <c r="C166" t="n">
-        <v>0.1473250251307975</v>
+        <v>0.1759053318919653</v>
       </c>
       <c r="D166" t="n">
-        <v>75.09445997850587</v>
+        <v>45.09712169851757</v>
       </c>
       <c r="E166" t="n">
-        <v>94.90612418512647</v>
+        <v>54.72387945195314</v>
       </c>
       <c r="F166" t="n">
-        <v>39.4194393666338</v>
+        <v>11.84275923193414</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>3.318291457286432</v>
+        <v>1.66</v>
       </c>
       <c r="B167" t="n">
-        <v>0.1444239029275701</v>
+        <v>0.1716874282174227</v>
       </c>
       <c r="C167" t="n">
-        <v>0.1458792241214208</v>
+        <v>0.1724948244552273</v>
       </c>
       <c r="D167" t="n">
-        <v>74.82431423952679</v>
+        <v>44.49751132367057</v>
       </c>
       <c r="E167" t="n">
-        <v>93.52550729596987</v>
+        <v>54.64214434852671</v>
       </c>
       <c r="F167" t="n">
-        <v>39.51640300257034</v>
+        <v>11.7561181448666</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>3.338341708542714</v>
+        <v>1.67</v>
       </c>
       <c r="B168" t="n">
-        <v>0.1429893034817444</v>
+        <v>0.1682957479031912</v>
       </c>
       <c r="C168" t="n">
-        <v>0.1443825264705675</v>
+        <v>0.1690389173747228</v>
       </c>
       <c r="D168" t="n">
-        <v>74.52868837011874</v>
+        <v>43.88122607211854</v>
       </c>
       <c r="E168" t="n">
-        <v>92.10575042164166</v>
+        <v>54.55154013551107</v>
       </c>
       <c r="F168" t="n">
-        <v>39.5981045767744</v>
+        <v>11.66313644397874</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>3.358391959798995</v>
+        <v>1.68</v>
       </c>
       <c r="B169" t="n">
-        <v>0.1415321191956894</v>
+        <v>0.164930367732566</v>
       </c>
       <c r="C169" t="n">
-        <v>0.1428322791977125</v>
+        <v>0.1656122095872839</v>
       </c>
       <c r="D169" t="n">
-        <v>74.21223823134116</v>
+        <v>43.26124842157521</v>
       </c>
       <c r="E169" t="n">
-        <v>90.65109522289571</v>
+        <v>54.4523645750507</v>
       </c>
       <c r="F169" t="n">
-        <v>39.6667887401049</v>
+        <v>11.56720577144185</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>3.378442211055276</v>
+        <v>1.69</v>
       </c>
       <c r="B170" t="n">
-        <v>0.1400567182056315</v>
+        <v>0.1616067655629272</v>
       </c>
       <c r="C170" t="n">
-        <v>0.1412464217038002</v>
+        <v>0.1622207666386232</v>
       </c>
       <c r="D170" t="n">
-        <v>73.87705582255309</v>
+        <v>42.64178556901242</v>
       </c>
       <c r="E170" t="n">
-        <v>89.16561723304383</v>
+        <v>54.34491245154594</v>
       </c>
       <c r="F170" t="n">
-        <v>39.72338099501901</v>
+        <v>11.46944011491833</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>3.398492462311558</v>
+        <v>1.7</v>
       </c>
       <c r="B171" t="n">
-        <v>0.1385593577827048</v>
+        <v>0.1583247869990332</v>
       </c>
       <c r="C171" t="n">
-        <v>0.1396454235887236</v>
+        <v>0.1591931284650905</v>
       </c>
       <c r="D171" t="n">
-        <v>73.52098413399723</v>
+        <v>42.02299221965966</v>
       </c>
       <c r="E171" t="n">
-        <v>88.34824764065382</v>
+        <v>54.22947520118117</v>
       </c>
       <c r="F171" t="n">
-        <v>39.76653531380173</v>
+        <v>11.36988378996086</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>3.418542713567839</v>
+        <v>1.71</v>
       </c>
       <c r="B172" t="n">
-        <v>0.1370327795377925</v>
+        <v>0.156123723798601</v>
       </c>
       <c r="C172" t="n">
-        <v>0.1380389238045896</v>
+        <v>0.1573912501312906</v>
       </c>
       <c r="D172" t="n">
-        <v>73.1399428397545</v>
+        <v>41.6825376151373</v>
       </c>
       <c r="E172" t="n">
-        <v>88.38543997260547</v>
+        <v>54.1063405784344</v>
       </c>
       <c r="F172" t="n">
-        <v>39.79383170187703</v>
+        <v>11.34410905252767</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>3.43859296482412</v>
+        <v>1.72</v>
       </c>
       <c r="B173" t="n">
-        <v>0.1354727440861978</v>
+        <v>0.1539018035576711</v>
       </c>
       <c r="C173" t="n">
-        <v>0.1364506903338717</v>
+        <v>0.1552443849997751</v>
       </c>
       <c r="D173" t="n">
-        <v>72.73138154113852</v>
+        <v>41.32960886609538</v>
       </c>
       <c r="E173" t="n">
-        <v>88.38713880940394</v>
+        <v>53.97579235720844</v>
       </c>
       <c r="F173" t="n">
-        <v>39.80363536366247</v>
+        <v>11.31383586100117</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>3.458643216080402</v>
+        <v>1.73</v>
       </c>
       <c r="B174" t="n">
-        <v>0.1339006307074579</v>
+        <v>0.1514620370778629</v>
       </c>
       <c r="C174" t="n">
-        <v>0.1349006562417676</v>
+        <v>0.1529704756855492</v>
       </c>
       <c r="D174" t="n">
-        <v>72.30653086956167</v>
+        <v>40.91090019137746</v>
       </c>
       <c r="E174" t="n">
-        <v>88.35477714839791</v>
+        <v>53.83811006469156</v>
       </c>
       <c r="F174" t="n">
-        <v>39.80186485739275</v>
+        <v>11.26432754580862</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>3.478693467336683</v>
+        <v>1.74</v>
       </c>
       <c r="B175" t="n">
-        <v>0.1322879501576167</v>
+        <v>0.1489441484307171</v>
       </c>
       <c r="C175" t="n">
-        <v>0.1333461033923124</v>
+        <v>0.1504183449845093</v>
       </c>
       <c r="D175" t="n">
-        <v>71.8498039795862</v>
+        <v>40.46334976493821</v>
       </c>
       <c r="E175" t="n">
-        <v>88.28976253972618</v>
+        <v>53.69356874571415</v>
       </c>
       <c r="F175" t="n">
-        <v>39.77973456355102</v>
+        <v>11.20549930471438</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>3.498743718592965</v>
+        <v>1.75</v>
       </c>
       <c r="B176" t="n">
-        <v>0.1306503161766945</v>
+        <v>0.1463042119518265</v>
       </c>
       <c r="C176" t="n">
-        <v>0.1317846174041337</v>
+        <v>0.1478518680886645</v>
       </c>
       <c r="D176" t="n">
-        <v>71.36934908714848</v>
+        <v>39.97458989173806</v>
       </c>
       <c r="E176" t="n">
-        <v>88.1934755980929</v>
+        <v>53.54243875581484</v>
       </c>
       <c r="F176" t="n">
-        <v>39.74147659363189</v>
+        <v>11.13376876384749</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>3.518793969849246</v>
+        <v>1.76</v>
       </c>
       <c r="B177" t="n">
-        <v>0.1289885773132917</v>
+        <v>0.1436728335008239</v>
       </c>
       <c r="C177" t="n">
-        <v>0.1301669526377833</v>
+        <v>0.1451643384531563</v>
       </c>
       <c r="D177" t="n">
-        <v>70.86539803117068</v>
+        <v>39.47993816539722</v>
       </c>
       <c r="E177" t="n">
-        <v>88.06726873234339</v>
+        <v>53.38498558115404</v>
       </c>
       <c r="F177" t="n">
-        <v>39.6869936301439</v>
+        <v>11.0588320690942</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>3.538844221105527</v>
+        <v>1.77</v>
       </c>
       <c r="B178" t="n">
-        <v>0.1272960078018305</v>
+        <v>0.1411031439845572</v>
       </c>
       <c r="C178" t="n">
-        <v>0.1285447504552526</v>
+        <v>0.1425082465705735</v>
       </c>
       <c r="D178" t="n">
-        <v>70.33400829103927</v>
+        <v>38.99411749650356</v>
       </c>
       <c r="E178" t="n">
-        <v>87.91246507521106</v>
+        <v>53.22146968330826</v>
       </c>
       <c r="F178" t="n">
-        <v>39.61384021310362</v>
+        <v>10.98480859540223</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>3.558894472361809</v>
+        <v>1.78</v>
       </c>
       <c r="B179" t="n">
-        <v>0.1255865978524578</v>
+        <v>0.1386026315876707</v>
       </c>
       <c r="C179" t="n">
-        <v>0.1268775599973987</v>
+        <v>0.1398944768820245</v>
       </c>
       <c r="D179" t="n">
-        <v>69.78266403662009</v>
+        <v>38.51949789690347</v>
       </c>
       <c r="E179" t="n">
-        <v>87.73035759793716</v>
+        <v>53.0521463675211</v>
       </c>
       <c r="F179" t="n">
-        <v>39.52599281495456</v>
+        <v>10.91241192236389</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>3.57894472361809</v>
+        <v>1.79</v>
       </c>
       <c r="B180" t="n">
-        <v>0.1238512007086865</v>
+        <v>0.1386786952436378</v>
       </c>
       <c r="C180" t="n">
-        <v>0.1251929571343023</v>
+        <v>0.1399538901943947</v>
       </c>
       <c r="D180" t="n">
-        <v>69.20609604952048</v>
+        <v>38.75715742182793</v>
       </c>
       <c r="E180" t="n">
-        <v>87.52220839313128</v>
+        <v>52.87726567250503</v>
       </c>
       <c r="F180" t="n">
-        <v>39.42025902301766</v>
+        <v>11.04142379913563</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>3.598994974874372</v>
+        <v>1.8</v>
       </c>
       <c r="B181" t="n">
-        <v>0.1220995953609894</v>
+        <v>0.1414861050368696</v>
       </c>
       <c r="C181" t="n">
-        <v>0.1234874145599619</v>
+        <v>0.1428330620635273</v>
       </c>
       <c r="D181" t="n">
-        <v>68.60955523198994</v>
+        <v>39.7626605073425</v>
       </c>
       <c r="E181" t="n">
-        <v>87.28924811311364</v>
+        <v>52.69707228048402</v>
       </c>
       <c r="F181" t="n">
-        <v>39.29940506865904</v>
+        <v>11.39116314641121</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>3.619045226130653</v>
+        <v>1.81</v>
       </c>
       <c r="B182" t="n">
-        <v>0.120332351429814</v>
+        <v>0.1438732221490474</v>
       </c>
       <c r="C182" t="n">
-        <v>0.1217446614670393</v>
+        <v>0.1452224952381275</v>
       </c>
       <c r="D182" t="n">
-        <v>67.99321122761563</v>
+        <v>40.65815657038816</v>
       </c>
       <c r="E182" t="n">
-        <v>87.0326755488843</v>
+        <v>52.51180544578262</v>
       </c>
       <c r="F182" t="n">
-        <v>39.16333745901445</v>
+        <v>11.71241333727851</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>3.639095477386935</v>
+        <v>1.82</v>
       </c>
       <c r="B183" t="n">
-        <v>0.1185498577366614</v>
+        <v>0.1458913917271786</v>
       </c>
       <c r="C183" t="n">
-        <v>0.1200062389470957</v>
+        <v>0.1472542691851265</v>
       </c>
       <c r="D183" t="n">
-        <v>67.35713808714186</v>
+        <v>41.45626714524882</v>
       </c>
       <c r="E183" t="n">
-        <v>86.75365733827998</v>
+        <v>52.32724364920487</v>
       </c>
       <c r="F183" t="n">
-        <v>39.01190950114997</v>
+        <v>12.00830510571416</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>3.659145728643216</v>
+        <v>1.83</v>
       </c>
       <c r="B184" t="n">
-        <v>0.1167606215383172</v>
+        <v>0.1475556258941192</v>
       </c>
       <c r="C184" t="n">
-        <v>0.1182413636988206</v>
+        <v>0.1488965471685483</v>
       </c>
       <c r="D184" t="n">
-        <v>66.70605284151037</v>
+        <v>42.15955336717692</v>
       </c>
       <c r="E184" t="n">
-        <v>86.45332779084696</v>
+        <v>52.14617112519117</v>
       </c>
       <c r="F184" t="n">
-        <v>38.84767938496913</v>
+        <v>12.27911940998697</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>3.679195979899498</v>
+        <v>1.84</v>
       </c>
       <c r="B185" t="n">
-        <v>0.1149602669424296</v>
+        <v>0.1489139912456968</v>
       </c>
       <c r="C185" t="n">
-        <v>0.1164491215686573</v>
+        <v>0.1502015718675319</v>
       </c>
       <c r="D185" t="n">
-        <v>66.03737849669442</v>
+        <v>42.78016604905614</v>
       </c>
       <c r="E185" t="n">
-        <v>86.13323177636549</v>
+        <v>51.96274772611643</v>
       </c>
       <c r="F185" t="n">
-        <v>38.66899440487809</v>
+        <v>12.52796180311883</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>3.699246231155779</v>
+        <v>1.85</v>
       </c>
       <c r="B186" t="n">
-        <v>0.1131578167053326</v>
+        <v>0.1500064896142013</v>
       </c>
       <c r="C186" t="n">
-        <v>0.1146644073183875</v>
+        <v>0.15123761153263</v>
       </c>
       <c r="D186" t="n">
-        <v>65.35622188180574</v>
+        <v>43.32822674595551</v>
       </c>
       <c r="E186" t="n">
-        <v>85.81231467546864</v>
+        <v>52.54437072057627</v>
       </c>
       <c r="F186" t="n">
-        <v>38.47869283794473</v>
+        <v>12.75741770474678</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>3.71929648241206</v>
+        <v>1.86</v>
       </c>
       <c r="B187" t="n">
-        <v>0.1113514036201254</v>
+        <v>0.1508615917679824</v>
       </c>
       <c r="C187" t="n">
-        <v>0.1128639241290061</v>
+        <v>0.1520372092264261</v>
       </c>
       <c r="D187" t="n">
-        <v>64.66147903351053</v>
+        <v>43.81075817083155</v>
       </c>
       <c r="E187" t="n">
-        <v>85.47272304439231</v>
+        <v>53.12018224299223</v>
       </c>
       <c r="F187" t="n">
-        <v>38.27600170284506</v>
+        <v>12.96921962569416</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>3.739346733668341</v>
+        <v>1.87</v>
       </c>
       <c r="B188" t="n">
-        <v>0.1095435234351922</v>
+        <v>0.1514920534794511</v>
       </c>
       <c r="C188" t="n">
-        <v>0.1110445581113301</v>
+        <v>0.1526242612237182</v>
       </c>
       <c r="D188" t="n">
-        <v>63.95456982277028</v>
+        <v>44.2303726151277</v>
       </c>
       <c r="E188" t="n">
-        <v>85.11547108657483</v>
+        <v>53.67556981744327</v>
       </c>
       <c r="F188" t="n">
-        <v>38.06163595026763</v>
+        <v>13.16383215624374</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>3.759396984924623</v>
+        <v>1.88</v>
       </c>
       <c r="B189" t="n">
-        <v>0.1077417271531116</v>
+        <v>0.1518972403788702</v>
       </c>
       <c r="C189" t="n">
-        <v>0.1092192973306819</v>
+        <v>0.153014247180754</v>
       </c>
       <c r="D189" t="n">
-        <v>63.2399125959174</v>
+        <v>44.58583167455445</v>
       </c>
       <c r="E189" t="n">
-        <v>84.74154150367171</v>
+        <v>54.20965677580612</v>
       </c>
       <c r="F189" t="n">
-        <v>37.83812272229605</v>
+        <v>13.34058434539285</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>3.779447236180904</v>
+        <v>1.89</v>
       </c>
       <c r="B190" t="n">
-        <v>0.1059352858078032</v>
+        <v>0.1520681125348462</v>
       </c>
       <c r="C190" t="n">
-        <v>0.1074034577131811</v>
+        <v>0.1531942578724651</v>
       </c>
       <c r="D190" t="n">
-        <v>62.51123344579458</v>
+        <v>44.87341260611245</v>
       </c>
       <c r="E190" t="n">
-        <v>84.35188577526546</v>
+        <v>55.5681739675971</v>
       </c>
       <c r="F190" t="n">
-        <v>37.601613978662</v>
+        <v>13.49805006206679</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>3.799497487437186</v>
+        <v>1.9</v>
       </c>
       <c r="B191" t="n">
-        <v>0.1041477461859227</v>
+        <v>0.1519892703512443</v>
       </c>
       <c r="C191" t="n">
-        <v>0.1055759888073308</v>
+        <v>0.1531303058245757</v>
       </c>
       <c r="D191" t="n">
-        <v>61.78245715798466</v>
+        <v>45.08744962272164</v>
       </c>
       <c r="E191" t="n">
-        <v>83.94742449483863</v>
+        <v>57.1962650777197</v>
       </c>
       <c r="F191" t="n">
-        <v>37.36039592389964</v>
+        <v>13.63419190983963</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>3.819547738693467</v>
+        <v>1.91</v>
       </c>
       <c r="B192" t="n">
-        <v>0.1023616867896172</v>
+        <v>0.1516398843589794</v>
       </c>
       <c r="C192" t="n">
-        <v>0.103739603561114</v>
+        <v>0.1527953566274192</v>
       </c>
       <c r="D192" t="n">
-        <v>61.04337193923739</v>
+        <v>45.22056151958441</v>
       </c>
       <c r="E192" t="n">
-        <v>83.52904775803994</v>
+        <v>58.74183913576473</v>
       </c>
       <c r="F192" t="n">
-        <v>37.10825987995555</v>
+        <v>13.74641495989505</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>3.839597989949749</v>
+        <v>1.92</v>
       </c>
       <c r="B193" t="n">
-        <v>0.1005841793062624</v>
+        <v>0.1509947714458352</v>
       </c>
       <c r="C193" t="n">
-        <v>0.1019088784940978</v>
+        <v>0.1521726639589883</v>
       </c>
       <c r="D193" t="n">
-        <v>60.29823102800063</v>
+        <v>45.26393190865839</v>
       </c>
       <c r="E193" t="n">
-        <v>83.09761559545781</v>
+        <v>60.23918549135012</v>
       </c>
       <c r="F193" t="n">
-        <v>36.847706272181</v>
+        <v>13.83163873351287</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>3.85964824120603</v>
+        <v>1.93</v>
       </c>
       <c r="B194" t="n">
-        <v>0.09882768411280021</v>
+        <v>0.1497235229849283</v>
       </c>
       <c r="C194" t="n">
-        <v>0.1000892920072486</v>
+        <v>0.1512521419933684</v>
       </c>
       <c r="D194" t="n">
-        <v>59.55462349561085</v>
+        <v>45.11661265968642</v>
       </c>
       <c r="E194" t="n">
-        <v>82.65395844381909</v>
+        <v>61.64449951830797</v>
       </c>
       <c r="F194" t="n">
-        <v>36.58333895832556</v>
+        <v>13.85842660627835</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>3.879698492462311</v>
+        <v>1.94</v>
       </c>
       <c r="B195" t="n">
-        <v>0.09708493538648308</v>
+        <v>0.1477624123228936</v>
       </c>
       <c r="C195" t="n">
-        <v>0.09826655291165258</v>
+        <v>0.1499822866146802</v>
       </c>
       <c r="D195" t="n">
-        <v>58.80834546862476</v>
+        <v>44.75636856784401</v>
       </c>
       <c r="E195" t="n">
-        <v>82.19887765297683</v>
+        <v>62.92145705080587</v>
       </c>
       <c r="F195" t="n">
-        <v>36.3125768387122</v>
+        <v>13.81900274728531</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>3.899748743718593</v>
+        <v>1.95</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0953577592215139</v>
+        <v>0.14678787931457</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0964563338274044</v>
+        <v>0.1482037389125521</v>
       </c>
       <c r="D196" t="n">
-        <v>58.06063790259969</v>
+        <v>44.69036961458836</v>
       </c>
       <c r="E196" t="n">
-        <v>81.7331460205924</v>
+        <v>64.0493204145223</v>
       </c>
       <c r="F196" t="n">
-        <v>36.03616456472141</v>
+        <v>13.86975180389288</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>3.919798994974874</v>
+        <v>1.96</v>
       </c>
       <c r="B197" t="n">
-        <v>0.09364178838120822</v>
+        <v>0.14944388758823</v>
       </c>
       <c r="C197" t="n">
-        <v>0.09465772797357194</v>
+        <v>0.1500601339276069</v>
       </c>
       <c r="D197" t="n">
-        <v>57.30897428747696</v>
+        <v>45.73233403936152</v>
       </c>
       <c r="E197" t="n">
-        <v>81.2575083531239</v>
+        <v>65.00631084298981</v>
       </c>
       <c r="F197" t="n">
-        <v>35.75251227405387</v>
+        <v>14.2659129621285</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>3.939849246231156</v>
+        <v>1.97</v>
       </c>
       <c r="B198" t="n">
-        <v>0.09194687219294628</v>
+        <v>0.1522047622427018</v>
       </c>
       <c r="C198" t="n">
-        <v>0.09288172714227427</v>
+        <v>0.1528402603328657</v>
       </c>
       <c r="D198" t="n">
-        <v>56.55951849926608</v>
+        <v>46.81484676749339</v>
       </c>
       <c r="E198" t="n">
-        <v>80.77268204571455</v>
+        <v>65.77028806830555</v>
       </c>
       <c r="F198" t="n">
-        <v>35.46544713107591</v>
+        <v>14.67810411807833</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>3.959899497487437</v>
+        <v>1.98</v>
       </c>
       <c r="B199" t="n">
-        <v>0.09025818934896962</v>
+        <v>0.1550279153364849</v>
       </c>
       <c r="C199" t="n">
-        <v>0.09112103201589994</v>
+        <v>0.1557121509934638</v>
       </c>
       <c r="D199" t="n">
-        <v>55.80330480340457</v>
+        <v>47.92523337600728</v>
       </c>
       <c r="E199" t="n">
-        <v>80.27935768177325</v>
+        <v>66.40971333699957</v>
       </c>
       <c r="F199" t="n">
-        <v>35.16933972910822</v>
+        <v>15.102524825436</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>3.979949748743719</v>
+        <v>1.99</v>
       </c>
       <c r="B200" t="n">
-        <v>0.08858396442648606</v>
+        <v>0.1579007911074839</v>
       </c>
       <c r="C200" t="n">
-        <v>0.08938155499066043</v>
+        <v>0.1586528853044513</v>
       </c>
       <c r="D200" t="n">
-        <v>55.04550243877662</v>
+        <v>49.05988448882598</v>
       </c>
       <c r="E200" t="n">
-        <v>79.77819964470928</v>
+        <v>66.81674577970041</v>
       </c>
       <c r="F200" t="n">
-        <v>34.8673997168836</v>
+        <v>15.53816501658897</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B201" t="n">
-        <v>0.08691805196096854</v>
+        <v>0.1608342741863122</v>
       </c>
       <c r="C201" t="n">
-        <v>0.08766894694706617</v>
+        <v>0.1616127260724163</v>
       </c>
       <c r="D201" t="n">
-        <v>54.28240919539892</v>
+        <v>50.22243185999439</v>
       </c>
       <c r="E201" t="n">
-        <v>79.26984674053298</v>
+        <v>66.97156384948953</v>
       </c>
       <c r="F201" t="n">
-        <v>34.55725498553876</v>
+        <v>15.986296569228</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="B202" t="n">
+        <v>0.1637560849581598</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.1645783715977891</v>
+      </c>
+      <c r="D202" t="n">
+        <v>51.39047634205325</v>
+      </c>
+      <c r="E202" t="n">
+        <v>66.93907873694664</v>
+      </c>
+      <c r="F202" t="n">
+        <v>16.4398871587466</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="B203" t="n">
+        <v>0.1667119367361269</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.1675781076832595</v>
+      </c>
+      <c r="D203" t="n">
+        <v>52.57838053853877</v>
+      </c>
+      <c r="E203" t="n">
+        <v>66.64625785697594</v>
+      </c>
+      <c r="F203" t="n">
+        <v>16.90358050819982</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="B204" t="n">
+        <v>0.1696244040722828</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.1705263630192779</v>
+      </c>
+      <c r="D204" t="n">
+        <v>53.76176421466975</v>
+      </c>
+      <c r="E204" t="n">
+        <v>66.15044179267593</v>
+      </c>
+      <c r="F204" t="n">
+        <v>17.36959456393449</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="B205" t="n">
+        <v>0.1725470161056974</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.173476298513961</v>
+      </c>
+      <c r="D205" t="n">
+        <v>54.95747357901317</v>
+      </c>
+      <c r="E205" t="n">
+        <v>65.38511874375006</v>
+      </c>
+      <c r="F205" t="n">
+        <v>17.84337730308206</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="B206" t="n">
+        <v>0.1754105642890687</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.1763525765733872</v>
+      </c>
+      <c r="D206" t="n">
+        <v>56.1434046693554</v>
+      </c>
+      <c r="E206" t="n">
+        <v>64.37565576539951</v>
+      </c>
+      <c r="F206" t="n">
+        <v>18.31777576902985</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="B207" t="n">
+        <v>0.1782376749622591</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.1791965196282459</v>
+      </c>
+      <c r="D207" t="n">
+        <v>57.32655814124246</v>
+      </c>
+      <c r="E207" t="n">
+        <v>63.11449529634151</v>
+      </c>
+      <c r="F207" t="n">
+        <v>18.79503850316476</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="B208" t="n">
+        <v>0.1810293153639702</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.1819525714029252</v>
+      </c>
+      <c r="D208" t="n">
+        <v>58.50707592693416</v>
+      </c>
+      <c r="E208" t="n">
+        <v>61.95068689341478</v>
+      </c>
+      <c r="F208" t="n">
+        <v>19.27519900302252</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="B209" t="n">
+        <v>0.1837588367145969</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.184666757335693</v>
+      </c>
+      <c r="D209" t="n">
+        <v>59.67613762894288</v>
+      </c>
+      <c r="E209" t="n">
+        <v>63.17591601904898</v>
+      </c>
+      <c r="F209" t="n">
+        <v>19.75532475961931</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="B210" t="n">
+        <v>0.1864253974787714</v>
+      </c>
+      <c r="C210" t="n">
+        <v>0.18732808924086</v>
+      </c>
+      <c r="D210" t="n">
+        <v>60.83317768138927</v>
+      </c>
+      <c r="E210" t="n">
+        <v>64.36921816947343</v>
+      </c>
+      <c r="F210" t="n">
+        <v>20.23517294783959</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="B211" t="n">
+        <v>0.1890221509545205</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.189925931421872</v>
+      </c>
+      <c r="D211" t="n">
+        <v>61.97565631821303</v>
+      </c>
+      <c r="E211" t="n">
+        <v>65.52498383895633</v>
+      </c>
+      <c r="F211" t="n">
+        <v>20.71383731425692</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="B212" t="n">
+        <v>0.1915467048762582</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.1924642146930507</v>
+      </c>
+      <c r="D212" t="n">
+        <v>63.10245846758112</v>
+      </c>
+      <c r="E212" t="n">
+        <v>66.63787512737434</v>
+      </c>
+      <c r="F212" t="n">
+        <v>21.19087387323345</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="B213" t="n">
+        <v>0.1940059665923873</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.1949442550801381</v>
+      </c>
+      <c r="D213" t="n">
+        <v>64.21553226839875</v>
+      </c>
+      <c r="E213" t="n">
+        <v>67.71137539459858</v>
+      </c>
+      <c r="F213" t="n">
+        <v>21.66686509364067</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="B214" t="n">
+        <v>0.1963759296825417</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.1973438432269574</v>
+      </c>
+      <c r="D214" t="n">
+        <v>65.30658834471858</v>
+      </c>
+      <c r="E214" t="n">
+        <v>68.76443896303141</v>
+      </c>
+      <c r="F214" t="n">
+        <v>22.13893532875788</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="B215" t="n">
+        <v>0.1986531068151433</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.1996393519224418</v>
+      </c>
+      <c r="D215" t="n">
+        <v>66.37404323962319</v>
+      </c>
+      <c r="E215" t="n">
+        <v>69.76222116249913</v>
+      </c>
+      <c r="F215" t="n">
+        <v>22.60644013960383</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="B216" t="n">
+        <v>0.2008343032994077</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.2018329196250941</v>
+      </c>
+      <c r="D216" t="n">
+        <v>67.41638995111666</v>
+      </c>
+      <c r="E216" t="n">
+        <v>70.70047022362176</v>
+      </c>
+      <c r="F216" t="n">
+        <v>23.06875116818164</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="B217" t="n">
+        <v>0.2029182450223433</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.2039274295156555</v>
+      </c>
+      <c r="D217" t="n">
+        <v>68.43274922692885</v>
+      </c>
+      <c r="E217" t="n">
+        <v>71.60620974878481</v>
+      </c>
+      <c r="F217" t="n">
+        <v>23.52544626708102</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="B218" t="n">
+        <v>0.2049066298658514</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.2059262524400838</v>
+      </c>
+      <c r="D218" t="n">
+        <v>69.42324078220298</v>
+      </c>
+      <c r="E218" t="n">
+        <v>72.46097885150216</v>
+      </c>
+      <c r="F218" t="n">
+        <v>23.97644270100383</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="B219" t="n">
+        <v>0.2068015885169323</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.2078279402027512</v>
+      </c>
+      <c r="D219" t="n">
+        <v>70.38814224772003</v>
+      </c>
+      <c r="E219" t="n">
+        <v>73.30121154181684</v>
+      </c>
+      <c r="F219" t="n">
+        <v>24.42171328684065</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="B220" t="n">
+        <v>0.2086042305117661</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.2096219717513631</v>
+      </c>
+      <c r="D220" t="n">
+        <v>71.32739540199015</v>
+      </c>
+      <c r="E220" t="n">
+        <v>74.1273585430353</v>
+      </c>
+      <c r="F220" t="n">
+        <v>24.86111554785212</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="B221" t="n">
+        <v>0.2103141008298736</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.2113192389925736</v>
+      </c>
+      <c r="D221" t="n">
+        <v>72.24041154609542</v>
+      </c>
+      <c r="E221" t="n">
+        <v>74.93949664127003</v>
+      </c>
+      <c r="F221" t="n">
+        <v>25.29432089481861</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="B222" t="n">
+        <v>0.2119290543667069</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.2129422485081514</v>
+      </c>
+      <c r="D222" t="n">
+        <v>73.12601597672916</v>
+      </c>
+      <c r="E222" t="n">
+        <v>75.73780774126195</v>
+      </c>
+      <c r="F222" t="n">
+        <v>25.72079087400252</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="B223" t="n">
+        <v>0.2134487026258183</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.2144808370650594</v>
+      </c>
+      <c r="D223" t="n">
+        <v>73.98362945326279</v>
+      </c>
+      <c r="E223" t="n">
+        <v>76.49402003444048</v>
+      </c>
+      <c r="F223" t="n">
+        <v>26.14018994451232</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="B224" t="n">
+        <v>0.2148759996247432</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.2159229417473663</v>
+      </c>
+      <c r="D224" t="n">
+        <v>74.81383407902112</v>
+      </c>
+      <c r="E224" t="n">
+        <v>77.21351580523326</v>
+      </c>
+      <c r="F224" t="n">
+        <v>26.55259105689283</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="B225" t="n">
+        <v>0.2162125723019143</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.2172635282668016</v>
+      </c>
+      <c r="D225" t="n">
+        <v>75.61676628194007</v>
+      </c>
+      <c r="E225" t="n">
+        <v>78.39238815802794</v>
+      </c>
+      <c r="F225" t="n">
+        <v>26.95791198104552</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="B226" t="n">
+        <v>0.2174540548083722</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.2185169141351393</v>
+      </c>
+      <c r="D226" t="n">
+        <v>76.39046741583884</v>
+      </c>
+      <c r="E226" t="n">
+        <v>79.54120109877728</v>
+      </c>
+      <c r="F226" t="n">
+        <v>27.35532111224501</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="B227" t="n">
+        <v>0.218591791273827</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.2196945180319237</v>
+      </c>
+      <c r="D227" t="n">
+        <v>77.13143780874633</v>
+      </c>
+      <c r="E227" t="n">
+        <v>80.61899837554107</v>
+      </c>
+      <c r="F227" t="n">
+        <v>27.74342008480641</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="B228" t="n">
+        <v>0.2196165613078425</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.2208847371668247</v>
+      </c>
+      <c r="D228" t="n">
+        <v>77.83592365495979</v>
+      </c>
+      <c r="E228" t="n">
+        <v>81.65722628135619</v>
+      </c>
+      <c r="F228" t="n">
+        <v>28.12069643956923</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="B229" t="n">
+        <v>0.2216849566469225</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.2230012807778132</v>
+      </c>
+      <c r="D229" t="n">
+        <v>78.91511782510389</v>
+      </c>
+      <c r="E229" t="n">
+        <v>82.63967428710566</v>
+      </c>
+      <c r="F229" t="n">
+        <v>28.63618687732174</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="B230" t="n">
+        <v>0.2237383600446232</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.22502395110427</v>
+      </c>
+      <c r="D230" t="n">
+        <v>79.9954105893251</v>
+      </c>
+      <c r="E230" t="n">
+        <v>83.54434792064561</v>
+      </c>
+      <c r="F230" t="n">
+        <v>29.15551289570116</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="B231" t="n">
+        <v>0.2257027902289742</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.2269562961150688</v>
+      </c>
+      <c r="D231" t="n">
+        <v>81.05016495562018</v>
+      </c>
+      <c r="E231" t="n">
+        <v>84.36912263723961</v>
+      </c>
+      <c r="F231" t="n">
+        <v>29.66892909953106</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="B232" t="n">
+        <v>0.2275589837344962</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.2287775102520589</v>
+      </c>
+      <c r="D232" t="n">
+        <v>82.0720165679876</v>
+      </c>
+      <c r="E232" t="n">
+        <v>85.16686926863227</v>
+      </c>
+      <c r="F232" t="n">
+        <v>30.17360606178802</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="B233" t="n">
+        <v>0.2293119697209778</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.2305026991656453</v>
+      </c>
+      <c r="D233" t="n">
+        <v>83.06228013536619</v>
+      </c>
+      <c r="E233" t="n">
+        <v>85.88470040009607</v>
+      </c>
+      <c r="F233" t="n">
+        <v>30.66987212582328</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="B234" t="n">
+        <v>0.230998701395801</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.23216495528226</v>
+      </c>
+      <c r="D234" t="n">
+        <v>84.03391527193943</v>
+      </c>
+      <c r="E234" t="n">
+        <v>86.51849379960636</v>
+      </c>
+      <c r="F234" t="n">
+        <v>31.16238229674459</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="B235" t="n">
+        <v>0.2325650199444756</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.2337396212575099</v>
+      </c>
+      <c r="D235" t="n">
+        <v>84.96682491177124</v>
+      </c>
+      <c r="E235" t="n">
+        <v>87.09275068450732</v>
+      </c>
+      <c r="F235" t="n">
+        <v>31.64356302946485</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="B236" t="n">
+        <v>0.2340165288057185</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.2352375147799821</v>
+      </c>
+      <c r="D236" t="n">
+        <v>85.86250099385194</v>
+      </c>
+      <c r="E236" t="n">
+        <v>87.61468387419463</v>
+      </c>
+      <c r="F236" t="n">
+        <v>32.11378742960013</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="B237" t="n">
+        <v>0.2353891512388881</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.2366468392312714</v>
+      </c>
+      <c r="D237" t="n">
+        <v>86.73364237077527</v>
+      </c>
+      <c r="E237" t="n">
+        <v>88.05017882200133</v>
+      </c>
+      <c r="F237" t="n">
+        <v>32.57764748098955</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="B238" t="n">
+        <v>0.2366131278432333</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.237959734786914</v>
+      </c>
+      <c r="D238" t="n">
+        <v>87.55406644032607</v>
+      </c>
+      <c r="E238" t="n">
+        <v>88.41087011990135</v>
+      </c>
+      <c r="F238" t="n">
+        <v>33.02515003440466</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="B239" t="n">
+        <v>0.2377668387131459</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.2391746309516425</v>
+      </c>
+      <c r="D239" t="n">
+        <v>88.3522023544883</v>
+      </c>
+      <c r="E239" t="n">
+        <v>88.73213832624826</v>
+      </c>
+      <c r="F239" t="n">
+        <v>33.46682157589785</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="B240" t="n">
+        <v>0.238773463232627</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.2402524079268773</v>
+      </c>
+      <c r="D240" t="n">
+        <v>89.09905514339845</v>
+      </c>
+      <c r="E240" t="n">
+        <v>88.96614958110356</v>
+      </c>
+      <c r="F240" t="n">
+        <v>33.89152657162524</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="B241" t="n">
+        <v>0.2396900088542701</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.2412363773506152</v>
+      </c>
+      <c r="D241" t="n">
+        <v>89.81529737817168</v>
+      </c>
+      <c r="E241" t="n">
+        <v>89.12831367940545</v>
+      </c>
+      <c r="F241" t="n">
+        <v>34.30691650321096</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="B242" t="n">
+        <v>0.2404702495888828</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.2420819718467323</v>
+      </c>
+      <c r="D242" t="n">
+        <v>90.48311341874658</v>
+      </c>
+      <c r="E242" t="n">
+        <v>89.24800351430106</v>
+      </c>
+      <c r="F242" t="n">
+        <v>34.70601178832087</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="B243" t="n">
+        <v>0.2411534722903279</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.2428257237927876</v>
+      </c>
+      <c r="D243" t="n">
+        <v>91.1167088502871</v>
+      </c>
+      <c r="E243" t="n">
+        <v>89.5746103764627</v>
+      </c>
+      <c r="F243" t="n">
+        <v>35.09405256052754</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="B244" t="n">
+        <v>0.2416996533349207</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.2434433581189764</v>
+      </c>
+      <c r="D244" t="n">
+        <v>91.70044435121351</v>
+      </c>
+      <c r="E244" t="n">
+        <v>90.06437030093149</v>
+      </c>
+      <c r="F244" t="n">
+        <v>35.46482697539192</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="B245" t="n">
+        <v>0.2421546200467845</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.2439389443153014</v>
+      </c>
+      <c r="D245" t="n">
+        <v>92.2511363888091</v>
+      </c>
+      <c r="E245" t="n">
+        <v>90.46955496671735</v>
+      </c>
+      <c r="F245" t="n">
+        <v>35.82462744358156</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="B246" t="n">
+        <v>0.2424602907488382</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.2443339697192004</v>
+      </c>
+      <c r="D246" t="n">
+        <v>92.7461402633496</v>
+      </c>
+      <c r="E246" t="n">
+        <v>90.84549659541689</v>
+      </c>
+      <c r="F246" t="n">
+        <v>36.16446635523555</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="B247" t="n">
+        <v>0.2426931364598486</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.2445746573243168</v>
+      </c>
+      <c r="D247" t="n">
+        <v>93.21412784433646</v>
+      </c>
+      <c r="E247" t="n">
+        <v>91.13424776201684</v>
+      </c>
+      <c r="F247" t="n">
+        <v>36.49530346256802</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="B248" t="n">
+        <v>0.2427602908423342</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.2447534054396614</v>
+      </c>
+      <c r="D248" t="n">
+        <v>93.61894471888159</v>
+      </c>
+      <c r="E248" t="n">
+        <v>91.3464389655385</v>
+      </c>
+      <c r="F248" t="n">
+        <v>36.80279701307053</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="B249" t="n">
+        <v>0.2427780121247443</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.2447638231064859</v>
+      </c>
+      <c r="D249" t="n">
+        <v>94.00483055356212</v>
+      </c>
+      <c r="E249" t="n">
+        <v>91.52250806683753</v>
+      </c>
+      <c r="F249" t="n">
+        <v>37.1041069736463</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="B250" t="n">
+        <v>0.2426267515266726</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.244703201809863</v>
+      </c>
+      <c r="D250" t="n">
+        <v>94.32507728356711</v>
+      </c>
+      <c r="E250" t="n">
+        <v>91.61267844935303</v>
+      </c>
+      <c r="F250" t="n">
+        <v>37.38063274493983</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="B251" t="n">
+        <v>0.2424338564555746</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.2445086406910243</v>
+      </c>
+      <c r="D251" t="n">
+        <v>94.62860060452184</v>
+      </c>
+      <c r="E251" t="n">
+        <v>91.63442963723075</v>
+      </c>
+      <c r="F251" t="n">
+        <v>37.65152386019592</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="B252" t="n">
+        <v>0.2420817087453466</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.2441865927310361</v>
+      </c>
+      <c r="D252" t="n">
+        <v>94.86911226056526</v>
+      </c>
+      <c r="E252" t="n">
+        <v>91.61472764150685</v>
+      </c>
+      <c r="F252" t="n">
+        <v>37.89820928915233</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="B253" t="n">
+        <v>0.2416924605552537</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.2437953618698718</v>
+      </c>
+      <c r="D253" t="n">
+        <v>95.09392710495405</v>
+      </c>
+      <c r="E253" t="n">
+        <v>91.51145962199952</v>
+      </c>
+      <c r="F253" t="n">
+        <v>38.13936476306999</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="B254" t="n">
+        <v>0.2411654364976147</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.24324770207479</v>
+      </c>
+      <c r="D254" t="n">
+        <v>95.26310343299525</v>
+      </c>
+      <c r="E254" t="n">
+        <v>91.5481573891708</v>
+      </c>
+      <c r="F254" t="n">
+        <v>38.35883232825832</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="B255" t="n">
+        <v>0.2405851395630854</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.2426292158794704</v>
+      </c>
+      <c r="D255" t="n">
+        <v>95.40950749453809</v>
+      </c>
+      <c r="E255" t="n">
+        <v>91.92368296035286</v>
+      </c>
+      <c r="F255" t="n">
+        <v>38.56963262872618</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="B256" t="n">
+        <v>0.2399053085728106</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.2418988651756206</v>
+      </c>
+      <c r="D256" t="n">
+        <v>95.51447161275986</v>
+      </c>
+      <c r="E256" t="n">
+        <v>92.22414484534775</v>
+      </c>
+      <c r="F256" t="n">
+        <v>38.76408074965219</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="B257" t="n">
+        <v>0.2391426304902564</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.2410791258511667</v>
+      </c>
+      <c r="D257" t="n">
+        <v>95.58419927894779</v>
+      </c>
+      <c r="E257" t="n">
+        <v>92.43981346726608</v>
+      </c>
+      <c r="F257" t="n">
+        <v>38.94450635961682</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="B258" t="n">
+        <v>0.2383312150165313</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.2401753102655184</v>
+      </c>
+      <c r="D258" t="n">
+        <v>95.63198918813205</v>
+      </c>
+      <c r="E258" t="n">
+        <v>92.57157175281704</v>
+      </c>
+      <c r="F258" t="n">
+        <v>39.1161807582949</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="B259" t="n">
+        <v>0.237431877388938</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.2392261243648415</v>
+      </c>
+      <c r="D259" t="n">
+        <v>95.64182873091224</v>
+      </c>
+      <c r="E259" t="n">
+        <v>92.62044468359049</v>
+      </c>
+      <c r="F259" t="n">
+        <v>39.27242410689269</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="B260" t="n">
+        <v>0.2364723740657</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.2381895292333074</v>
+      </c>
+      <c r="D260" t="n">
+        <v>95.62453022288636</v>
+      </c>
+      <c r="E260" t="n">
+        <v>92.6403179134262</v>
+      </c>
+      <c r="F260" t="n">
+        <v>39.4175121644549</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="B261" t="n">
+        <v>0.2354782530313751</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.2371007255416721</v>
+      </c>
+      <c r="D261" t="n">
+        <v>95.59018281627429</v>
+      </c>
+      <c r="E261" t="n">
+        <v>93.16580163365462</v>
+      </c>
+      <c r="F261" t="n">
+        <v>39.55549027629682</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="B262" t="n">
+        <v>0.2344258467055776</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.2359732528193385</v>
+      </c>
+      <c r="D262" t="n">
+        <v>95.52897977998029</v>
+      </c>
+      <c r="E262" t="n">
+        <v>94.03503131836014</v>
+      </c>
+      <c r="F262" t="n">
+        <v>39.68220337873002</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="B263" t="n">
+        <v>0.2333246689154724</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.2347906709350616</v>
+      </c>
+      <c r="D263" t="n">
+        <v>95.44453986653446</v>
+      </c>
+      <c r="E263" t="n">
+        <v>94.85962431160034</v>
+      </c>
+      <c r="F263" t="n">
+        <v>39.79903221453292</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="B264" t="n">
+        <v>0.2321814465488755</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.2335676174869426</v>
+      </c>
+      <c r="D264" t="n">
+        <v>95.33939685894632</v>
+      </c>
+      <c r="E264" t="n">
+        <v>95.63953000508948</v>
+      </c>
+      <c r="F264" t="n">
+        <v>39.90692642034822</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="B265" t="n">
+        <v>0.2310063919406567</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.232318263432659</v>
+      </c>
+      <c r="D265" t="n">
+        <v>95.21756320316823</v>
+      </c>
+      <c r="E265" t="n">
+        <v>96.3747603888196</v>
+      </c>
+      <c r="F265" t="n">
+        <v>40.00747305178585</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="B266" t="n">
+        <v>0.229806771669768</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.2310563194584294</v>
+      </c>
+      <c r="D266" t="n">
+        <v>95.08189632552518</v>
+      </c>
+      <c r="E266" t="n">
+        <v>97.06538724393951</v>
+      </c>
+      <c r="F266" t="n">
+        <v>40.1017975667099</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="B267" t="n">
+        <v>0.2285635016693654</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.2297826214017772</v>
+      </c>
+      <c r="D267" t="n">
+        <v>94.92435538780379</v>
+      </c>
+      <c r="E267" t="n">
+        <v>97.71153935987242</v>
+      </c>
+      <c r="F267" t="n">
+        <v>40.18642981021681</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="B268" t="n">
+        <v>0.2272732942782452</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.2284898938293575</v>
+      </c>
+      <c r="D268" t="n">
+        <v>94.74336541116509</v>
+      </c>
+      <c r="E268" t="n">
+        <v>98.3133997776881</v>
+      </c>
+      <c r="F268" t="n">
+        <v>40.26059606403084</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="B269" t="n">
+        <v>0.2259354555306554</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.2271794774964207</v>
+      </c>
+      <c r="D269" t="n">
+        <v>94.53841616732022</v>
+      </c>
+      <c r="E269" t="n">
+        <v>98.87120306871054</v>
+      </c>
+      <c r="F269" t="n">
+        <v>40.32396673688881</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="B270" t="n">
+        <v>0.2245793862124074</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.2258469846837085</v>
+      </c>
+      <c r="D270" t="n">
+        <v>94.32163266056624</v>
+      </c>
+      <c r="E270" t="n">
+        <v>99.38523265201515</v>
+      </c>
+      <c r="F270" t="n">
+        <v>40.38161847096883</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="B271" t="n">
+        <v>0.223182897364136</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.2244754467398148</v>
+      </c>
+      <c r="D271" t="n">
+        <v>94.0835756623167</v>
+      </c>
+      <c r="E271" t="n">
+        <v>99.85581815565507</v>
+      </c>
+      <c r="F271" t="n">
+        <v>40.42943855212871</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="B272" t="n">
+        <v>0.2217384436214728</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.2230353210161983</v>
+      </c>
+      <c r="D272" t="n">
+        <v>93.82086329342008</v>
+      </c>
+      <c r="E272" t="n">
+        <v>100.2833328258729</v>
+      </c>
+      <c r="F272" t="n">
+        <v>40.46586676898423</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="B273" t="n">
+        <v>0.2202474910959364</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.2215715495297857</v>
+      </c>
+      <c r="D273" t="n">
+        <v>93.53389351251099</v>
+      </c>
+      <c r="E273" t="n">
+        <v>100.6752753655882</v>
+      </c>
+      <c r="F273" t="n">
+        <v>40.49095767768007</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="B274" t="n">
+        <v>0.2187480057018481</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.2200747110362584</v>
+      </c>
+      <c r="D274" t="n">
+        <v>93.23863102380183</v>
+      </c>
+      <c r="E274" t="n">
+        <v>101.055205463467</v>
+      </c>
+      <c r="F274" t="n">
+        <v>40.51153200974718</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="B275" t="n">
+        <v>0.2172041398114523</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.218527482496908</v>
+      </c>
+      <c r="D275" t="n">
+        <v>92.91970028285975</v>
+      </c>
+      <c r="E275" t="n">
+        <v>101.3932036479612</v>
+      </c>
+      <c r="F275" t="n">
+        <v>40.52084513313857</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="B276" t="n">
+        <v>0.2156239408627099</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.2169466743065962</v>
+      </c>
+      <c r="D276" t="n">
+        <v>92.58034866450414</v>
+      </c>
+      <c r="E276" t="n">
+        <v>101.6897658605978</v>
+      </c>
+      <c r="F276" t="n">
+        <v>40.5202053385992</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="B277" t="n">
+        <v>0.21401681841429</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.2153456914342773</v>
+      </c>
+      <c r="D277" t="n">
+        <v>92.2244607689131</v>
+      </c>
+      <c r="E277" t="n">
+        <v>102.0512541553614</v>
+      </c>
+      <c r="F277" t="n">
+        <v>40.5112215027856</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="B278" t="n">
+        <v>0.2123994589977223</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.2136939798884782</v>
+      </c>
+      <c r="D278" t="n">
+        <v>91.85912712730756</v>
+      </c>
+      <c r="E278" t="n">
+        <v>102.7473696945312</v>
+      </c>
+      <c r="F278" t="n">
+        <v>40.49694059665735</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="B279" t="n">
+        <v>0.2107716380676727</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.2120098882067793</v>
+      </c>
+      <c r="D279" t="n">
+        <v>91.48420232785062</v>
+      </c>
+      <c r="E279" t="n">
+        <v>103.4014657811439</v>
+      </c>
+      <c r="F279" t="n">
+        <v>40.47725318252428</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="B280" t="n">
+        <v>0.2091336951448507</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.2103101241836119</v>
+      </c>
+      <c r="D280" t="n">
+        <v>91.09978526662998</v>
+      </c>
+      <c r="E280" t="n">
+        <v>104.0138117529513</v>
+      </c>
+      <c r="F280" t="n">
+        <v>40.45215738002632</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="B281" t="n">
+        <v>0.20749228253925</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.2085907984561695</v>
+      </c>
+      <c r="D281" t="n">
+        <v>90.70873670199742</v>
+      </c>
+      <c r="E281" t="n">
+        <v>104.5847165624014</v>
+      </c>
+      <c r="F281" t="n">
+        <v>40.42288271768353</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="B282" t="n">
+        <v>0.2058510490109046</v>
+      </c>
+      <c r="C282" t="n">
+        <v>0.2068783064748387</v>
+      </c>
+      <c r="D282" t="n">
+        <v>90.31264119578687</v>
+      </c>
+      <c r="E282" t="n">
+        <v>105.1145265870517</v>
+      </c>
+      <c r="F282" t="n">
+        <v>40.39010618868376</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="B283" t="n">
+        <v>0.2042107495016706</v>
+      </c>
+      <c r="C283" t="n">
+        <v>0.2051759083695911</v>
+      </c>
+      <c r="D283" t="n">
+        <v>89.91183197969382</v>
+      </c>
+      <c r="E283" t="n">
+        <v>105.6036234853711</v>
+      </c>
+      <c r="F283" t="n">
+        <v>40.35395325568575</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="B284" t="n">
+        <v>0.2025711855804865</v>
+      </c>
+      <c r="C284" t="n">
+        <v>0.2035003822844369</v>
+      </c>
+      <c r="D284" t="n">
+        <v>89.5062257516894</v>
+      </c>
+      <c r="E284" t="n">
+        <v>106.052422100685</v>
+      </c>
+      <c r="F284" t="n">
+        <v>40.3143638924417</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="B285" t="n">
+        <v>0.2009321514216738</v>
+      </c>
+      <c r="C285" t="n">
+        <v>0.2018549407971205</v>
+      </c>
+      <c r="D285" t="n">
+        <v>89.09573469163315</v>
+      </c>
+      <c r="E285" t="n">
+        <v>106.4613684155638</v>
+      </c>
+      <c r="F285" t="n">
+        <v>40.27127550020004</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="B286" t="n">
+        <v>0.1992934346866353</v>
+      </c>
+      <c r="C286" t="n">
+        <v>0.2002167974124548</v>
+      </c>
+      <c r="D286" t="n">
+        <v>88.68026679587848</v>
+      </c>
+      <c r="E286" t="n">
+        <v>106.8309375571636</v>
+      </c>
+      <c r="F286" t="n">
+        <v>40.22462302352558</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="B287" t="n">
+        <v>0.1976555178020317</v>
+      </c>
+      <c r="C287" t="n">
+        <v>0.1985783513447746</v>
+      </c>
+      <c r="D287" t="n">
+        <v>88.26003897143983</v>
+      </c>
+      <c r="E287" t="n">
+        <v>107.1616318559664</v>
+      </c>
+      <c r="F287" t="n">
+        <v>40.1744814321936</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="B288" t="n">
+        <v>0.196020248123222</v>
+      </c>
+      <c r="C288" t="n">
+        <v>0.196939353092878</v>
+      </c>
+      <c r="D288" t="n">
+        <v>87.83588275724775</v>
+      </c>
+      <c r="E288" t="n">
+        <v>107.453978958262</v>
+      </c>
+      <c r="F288" t="n">
+        <v>40.12120782515317</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="B289" t="n">
+        <v>0.1943900963546826</v>
+      </c>
+      <c r="C289" t="n">
+        <v>0.1952995496155679</v>
+      </c>
+      <c r="D289" t="n">
+        <v>87.40892152287755</v>
+      </c>
+      <c r="E289" t="n">
+        <v>107.7085299940831</v>
+      </c>
+      <c r="F289" t="n">
+        <v>40.06529836040886</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="B290" t="n">
+        <v>0.1927660957729079</v>
+      </c>
+      <c r="C290" t="n">
+        <v>0.1936586850570875</v>
+      </c>
+      <c r="D290" t="n">
+        <v>86.9796454738229</v>
+      </c>
+      <c r="E290" t="n">
+        <v>107.9349597408737</v>
+      </c>
+      <c r="F290" t="n">
+        <v>40.0069651188092</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="B291" t="n">
+        <v>0.1911459777629234</v>
+      </c>
+      <c r="C291" t="n">
+        <v>0.192023471469077</v>
+      </c>
+      <c r="D291" t="n">
+        <v>86.54705623855607</v>
+      </c>
+      <c r="E291" t="n">
+        <v>108.1504090318725</v>
+      </c>
+      <c r="F291" t="n">
+        <v>39.94573625021352</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="B292" t="n">
+        <v>0.1895250545280596</v>
+      </c>
+      <c r="C292" t="n">
+        <v>0.1904018493888956</v>
+      </c>
+      <c r="D292" t="n">
+        <v>86.10904214357163</v>
+      </c>
+      <c r="E292" t="n">
+        <v>108.3295077764139</v>
+      </c>
+      <c r="F292" t="n">
+        <v>39.88061793298808</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="B293" t="n">
+        <v>0.1878982001538912</v>
+      </c>
+      <c r="C293" t="n">
+        <v>0.1887960204936598</v>
+      </c>
+      <c r="D293" t="n">
+        <v>85.66326249996125</v>
+      </c>
+      <c r="E293" t="n">
+        <v>108.472867199305</v>
+      </c>
+      <c r="F293" t="n">
+        <v>39.81049647128248</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="B294" t="n">
+        <v>0.1862604334992397</v>
+      </c>
+      <c r="C294" t="n">
+        <v>0.1871945335224549</v>
+      </c>
+      <c r="D294" t="n">
+        <v>85.20741083477449</v>
+      </c>
+      <c r="E294" t="n">
+        <v>108.5811146490522</v>
+      </c>
+      <c r="F294" t="n">
+        <v>39.7342592236797</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="B295" t="n">
+        <v>0.1846069168156988</v>
+      </c>
+      <c r="C295" t="n">
+        <v>0.1855776889497443</v>
+      </c>
+      <c r="D295" t="n">
+        <v>84.73921538752597</v>
+      </c>
+      <c r="E295" t="n">
+        <v>108.654892079977</v>
+      </c>
+      <c r="F295" t="n">
+        <v>39.65079510780146</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="B296" t="n">
+        <v>0.1829353335000104</v>
+      </c>
+      <c r="C296" t="n">
+        <v>0.1839528149574151</v>
+      </c>
+      <c r="D296" t="n">
+        <v>84.25753539011828</v>
+      </c>
+      <c r="E296" t="n">
+        <v>108.6948545899452</v>
+      </c>
+      <c r="F296" t="n">
+        <v>39.55950958772901</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="B297" t="n">
+        <v>0.1812673318784088</v>
+      </c>
+      <c r="C297" t="n">
+        <v>0.182317162312548</v>
+      </c>
+      <c r="D297" t="n">
+        <v>83.77229094513541</v>
+      </c>
+      <c r="E297" t="n">
+        <v>108.7016690127389</v>
+      </c>
+      <c r="F297" t="n">
+        <v>39.46501162623015</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="B298" t="n">
+        <v>0.1795762687166015</v>
+      </c>
+      <c r="C298" t="n">
+        <v>0.1806521785401685</v>
+      </c>
+      <c r="D298" t="n">
+        <v>83.27114411965157</v>
+      </c>
+      <c r="E298" t="n">
+        <v>108.6760125650149</v>
+      </c>
+      <c r="F298" t="n">
+        <v>39.36145218457367</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="B299" t="n">
+        <v>0.1778636943890952</v>
+      </c>
+      <c r="C299" t="n">
+        <v>0.1789710445399442</v>
+      </c>
+      <c r="D299" t="n">
+        <v>82.75470823835938</v>
+      </c>
+      <c r="E299" t="n">
+        <v>108.6185715468501</v>
+      </c>
+      <c r="F299" t="n">
+        <v>39.24904622318222</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="B300" t="n">
+        <v>0.1761430057893124</v>
+      </c>
+      <c r="C300" t="n">
+        <v>0.1772802219742353</v>
+      </c>
+      <c r="D300" t="n">
+        <v>82.22913663882905</v>
+      </c>
+      <c r="E300" t="n">
+        <v>108.53004009563</v>
+      </c>
+      <c r="F300" t="n">
+        <v>39.13064895112308</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>3</v>
+      </c>
+      <c r="B301" t="n">
+        <v>0.1744232203809377</v>
+      </c>
+      <c r="C301" t="n">
+        <v>0.1755514610346004</v>
+      </c>
+      <c r="D301" t="n">
+        <v>81.69861503122272</v>
+      </c>
+      <c r="E301" t="n">
+        <v>108.4111189923224</v>
+      </c>
+      <c r="F301" t="n">
+        <v>39.00821527794275</v>
       </c>
     </row>
   </sheetData>
